--- a/105118麻醉学考研三年数据统计表.xlsx
+++ b/105118麻醉学考研三年数据统计表.xlsx
@@ -16,11 +16,11 @@
     <sheet name="数据来源与说明" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'三年复试线对比'!$A$2:$L$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'三年复试线对比'!$A$2:$M$93</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2026复试线明细'!$A$2:$F$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2025录取明细'!$A$2:$I$153</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2024复试线明细'!$A$2:$I$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'麻醉学专业排名'!$A$2:$F$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2024复试线明细'!$A$2:$J$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'麻醉学专业排名'!$A$2:$G$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1273,21 +1273,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="52" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1315,45 +1316,50 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
           <t>院校层次</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>2024复试线</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>2025复试线</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>2026复试线</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>2026单科线(政/外/专)</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>2026较2024变化</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>2026高出A区国家线</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>数据性质</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1375,29 +1381,34 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
           <t>985/双一流</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n">
         <v>310</v>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>55/55/180</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>医学门类专硕校线，麻醉学按1051执行；实际录取分远高于校线</t>
         </is>
@@ -1419,29 +1430,34 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
           <t>双一流</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n">
         <v>330</v>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>2026年统考计划7人</t>
         </is>
@@ -1463,35 +1479,40 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
           <t>双一流</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="F5" s="5" t="n">
         <v>340</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>330</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>330</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="5" t="n">
+        <v>330</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>45/190</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="J5" s="5" t="n">
         <v>-10</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="K5" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>2024年拟录取16人最低342；2025年录取12人均分358；2026统考可招约10人</t>
         </is>
@@ -1513,29 +1534,34 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>211/双一流</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="F6" s="5" t="n">
         <v>344</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <v>361</v>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>50/50/170</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>2025年专硕361分；2026年计划扩至17人（2025年10人）</t>
         </is>
@@ -1557,29 +1583,34 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>2025年录取44人均分362</t>
         </is>
@@ -1601,25 +1632,30 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>承德</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr">
+      <c r="M8" s="6" t="inlineStr">
         <is>
           <t>2025年录取约10人均分335（循国家A线）</t>
         </is>
@@ -1641,29 +1677,34 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="F9" s="5" t="n">
         <v>343</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="G9" s="5" t="n">
         <v>331</v>
       </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>校自划线</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="M9" s="6" t="inlineStr">
         <is>
           <t>2024年首次招生343；2025年录取31人均分351</t>
         </is>
@@ -1685,29 +1726,34 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>长治</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>304</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="G10" s="5" t="n">
+        <v>304</v>
+      </c>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>36/108</t>
         </is>
       </c>
-      <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>校自划线</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="M10" s="6" t="inlineStr">
         <is>
           <t>2025年麻醉学自划线304，高于当年国家线11分</t>
         </is>
@@ -1729,29 +1775,34 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>B区省属</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="G11" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>33/99</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>2025年录取43人均分335；2026年一临录取5人均分330</t>
         </is>
@@ -1773,35 +1824,40 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>310</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <v>305</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="H12" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="J12" s="5" t="n">
         <v>-16</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="K12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>校自划线</t>
         </is>
       </c>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="M12" s="6" t="inlineStr">
         <is>
           <t>2026年为1051校线；2025年录取42人均分363；306单科要求170分</t>
         </is>
@@ -1823,29 +1879,34 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>大连</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="F13" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="G13" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr">
         <is>
           <t>2025年录取48人均分340</t>
         </is>
@@ -1867,29 +1928,34 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>锦州</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="F14" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L14" s="6" t="inlineStr">
+      <c r="M14" s="6" t="inlineStr">
         <is>
           <t>2025年录取42人均分332</t>
         </is>
@@ -1911,29 +1977,34 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="G15" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1955,27 +2026,32 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>310</v>
       </c>
-      <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>校线(1051)</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="M16" s="6" t="inlineStr">
         <is>
           <t>2024年麻醉学调剂录取分383-389，调剂门槛极高</t>
         </is>
@@ -1997,25 +2073,30 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>佳木斯</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="M17" s="6" t="inlineStr">
         <is>
           <t>2025年录取约9人均分356（原表数据不完整）</t>
         </is>
@@ -2037,29 +2118,34 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>齐齐哈尔</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="F18" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="G18" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr">
+      <c r="M18" s="6" t="inlineStr">
         <is>
           <t>2025年录取5人均分354</t>
         </is>
@@ -2081,35 +2167,40 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="F19" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="G19" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="H19" s="5" t="n">
         <v>322</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="J19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="K19" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L19" s="6" t="inlineStr">
+      <c r="M19" s="6" t="inlineStr">
         <is>
           <t>2026年麻醉学（附属红旗医院基地）322分</t>
         </is>
@@ -2131,29 +2222,34 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n">
         <v>320</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n">
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L20" s="6" t="inlineStr">
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>2025年录取28人均分375</t>
         </is>
@@ -2175,27 +2271,32 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>延吉</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="F21" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L21" s="6" t="inlineStr">
+      <c r="M21" s="6" t="inlineStr">
         <is>
           <t>2025年录取37人均分336</t>
         </is>
@@ -2217,29 +2318,34 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n">
         <v>320</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>50/50/180</t>
         </is>
       </c>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n">
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L22" s="6" t="inlineStr">
+      <c r="M22" s="6" t="inlineStr">
         <is>
           <t>1051专硕校线；麻醉统招约8人，实际录取远高于校线</t>
         </is>
@@ -2261,29 +2367,34 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n">
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n">
         <v>330</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>60/60/190</t>
         </is>
       </c>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n">
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L23" s="6" t="inlineStr">
+      <c r="M23" s="6" t="inlineStr">
         <is>
           <t>1051专硕校线；2025年瑞金医院麻醉录取1人352</t>
         </is>
@@ -2305,29 +2416,34 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n">
         <v>365</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>55/55/190</t>
         </is>
       </c>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n">
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L24" s="6" t="inlineStr">
+      <c r="M24" s="6" t="inlineStr">
         <is>
           <t>2025年专硕录取13人；2026年专硕计划13人</t>
         </is>
@@ -2349,25 +2465,30 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>211/军队</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L25" s="6" t="inlineStr">
+      <c r="M25" s="6" t="inlineStr">
         <is>
           <t>2025年录取1人353分</t>
         </is>
@@ -2389,29 +2510,34 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="F26" s="5" t="n">
         <v>347</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="G26" s="5" t="n">
         <v>318</v>
       </c>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L26" s="6" t="inlineStr">
+      <c r="M26" s="6" t="inlineStr">
         <is>
           <t>2024年录取10人；2025年专硕录取6人，线降29分</t>
         </is>
@@ -2433,29 +2559,34 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n">
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n">
         <v>367</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>50/50/180</t>
         </is>
       </c>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n">
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L27" s="6" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr">
         <is>
           <t>2026年第一临床367、四临（肿瘤337/妇产354）；2025年录取34人均分365</t>
         </is>
@@ -2477,35 +2608,40 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>镇江</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="F28" s="5" t="n">
         <v>327</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="G28" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="H28" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>36/36/108</t>
         </is>
       </c>
-      <c r="I28" s="5" t="n">
+      <c r="J28" s="5" t="n">
         <v>-33</v>
       </c>
-      <c r="J28" s="5" t="n">
+      <c r="K28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L28" s="6" t="inlineStr">
+      <c r="M28" s="6" t="inlineStr">
         <is>
           <t>2026年招生7人；2025年录取8人均分345</t>
         </is>
@@ -2527,35 +2663,40 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>无锡</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="F29" s="5" t="n">
         <v>319</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="G29" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="H29" s="5" t="n">
         <v>335</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="J29" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="K29" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L29" s="6" t="inlineStr">
+      <c r="M29" s="6" t="inlineStr">
         <is>
           <t>2026年无锡医学院335；2025年录取9人均分337</t>
         </is>
@@ -2577,29 +2718,34 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="F30" s="5" t="n">
         <v>308</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="G30" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L30" s="6" t="inlineStr">
+      <c r="M30" s="6" t="inlineStr">
         <is>
           <t>2025年录取19人均分341</t>
         </is>
@@ -2621,35 +2767,40 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
+          <t>扬州</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="F31" s="5" t="n">
         <v>310</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="G31" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="H31" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>36/36/108</t>
         </is>
       </c>
-      <c r="I31" s="5" t="n">
+      <c r="J31" s="5" t="n">
         <v>-16</v>
       </c>
-      <c r="J31" s="5" t="n">
+      <c r="K31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="M31" s="6" t="inlineStr">
         <is>
           <t>2025年录取8人均分333</t>
         </is>
@@ -2671,35 +2822,40 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
+          <t>徐州</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="F32" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="G32" s="5" t="n">
         <v>342</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="H32" s="5" t="n">
         <v>332</v>
       </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>36/36/108</t>
         </is>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="J32" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="J32" s="5" t="n">
+      <c r="K32" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L32" s="6" t="inlineStr">
+      <c r="M32" s="6" t="inlineStr">
         <is>
           <t>麻醉学院332；2026年盐城临床362/淮安358/连云港352；麻醉学全国第一</t>
         </is>
@@ -2721,25 +2877,30 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="5" t="n"/>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I33" s="5" t="n"/>
       <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L33" s="6" t="inlineStr">
+      <c r="M33" s="6" t="inlineStr">
         <is>
           <t>2025年录取6人均分383，为全国最高梯队</t>
         </is>
@@ -2761,35 +2922,40 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
+          <t>温州</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>345</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>345</v>
       </c>
       <c r="G34" s="5" t="n">
+        <v>345</v>
+      </c>
+      <c r="H34" s="5" t="n">
         <v>350</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I34" s="5" t="n">
+      <c r="J34" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J34" s="5" t="n">
+      <c r="K34" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L34" s="6" t="inlineStr">
+      <c r="M34" s="6" t="inlineStr">
         <is>
           <t>2024年录取9人最低349最高420均分373；2025年录取47人均分351</t>
         </is>
@@ -2811,29 +2977,34 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>双一流</t>
         </is>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="F35" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="G35" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I35" s="5" t="n"/>
       <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L35" s="6" t="inlineStr">
+      <c r="M35" s="6" t="inlineStr">
         <is>
           <t>2025年录取13人均分352</t>
         </is>
@@ -2855,35 +3026,40 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>湖州</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="F36" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="G36" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="H36" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>36/36/108</t>
         </is>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="J36" s="5" t="n">
         <v>-10</v>
       </c>
-      <c r="J36" s="5" t="n">
+      <c r="K36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L36" s="6" t="inlineStr">
+      <c r="M36" s="6" t="inlineStr">
         <is>
           <t>2025年录取5人均分356</t>
         </is>
@@ -2905,29 +3081,34 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
+          <t>绍兴</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="F37" s="5" t="n">
         <v>317</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="G37" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I37" s="5" t="n"/>
       <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L37" s="6" t="inlineStr">
+      <c r="M37" s="6" t="inlineStr">
         <is>
           <t>2024年录取6人均分334.8；2026年录取5人均分335.6</t>
         </is>
@@ -2949,29 +3130,34 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="F38" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="G38" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="6" t="inlineStr">
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I38" s="5" t="n"/>
       <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L38" s="6" t="inlineStr">
+      <c r="M38" s="6" t="inlineStr">
         <is>
           <t>2026年录取2人最低359；2025年录取3人均分344</t>
         </is>
@@ -2993,29 +3179,34 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="F39" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="G39" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I39" s="5" t="n"/>
       <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L39" s="6" t="inlineStr">
+      <c r="M39" s="6" t="inlineStr">
         <is>
           <t>2025年录取47人均分360</t>
         </is>
@@ -3037,29 +3228,34 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>芜湖</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="F40" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="G40" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I40" s="5" t="n"/>
       <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L40" s="6" t="inlineStr">
+      <c r="M40" s="6" t="inlineStr">
         <is>
           <t>2025年录取42人均分335</t>
         </is>
@@ -3081,29 +3277,34 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>蚌埠</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="F41" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="G41" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I41" s="5" t="n"/>
       <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L41" s="6" t="inlineStr">
+      <c r="M41" s="6" t="inlineStr">
         <is>
           <t>2025年录取29人均分349；2026年录取14人均分330</t>
         </is>
@@ -3125,29 +3326,34 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="F42" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="G42" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I42" s="5" t="n"/>
       <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L42" s="6" t="inlineStr">
+      <c r="M42" s="6" t="inlineStr">
         <is>
           <t>2025年录取61人均分359；2026年录取27人均分340</t>
         </is>
@@ -3169,29 +3375,34 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>赣州</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="F43" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="G43" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I43" s="5" t="n"/>
       <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L43" s="6" t="inlineStr">
+      <c r="M43" s="6" t="inlineStr">
         <is>
           <t>2025年录取14人均分342</t>
         </is>
@@ -3213,35 +3424,40 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="F44" s="5" t="n">
         <v>315</v>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="G44" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G44" s="5" t="n">
+      <c r="H44" s="5" t="n">
         <v>350</v>
       </c>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>55/55/165</t>
         </is>
       </c>
-      <c r="I44" s="5" t="n">
+      <c r="J44" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="J44" s="5" t="n">
+      <c r="K44" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L44" s="6" t="inlineStr">
+      <c r="M44" s="6" t="inlineStr">
         <is>
           <t>2025年录取34人均分369；2026年麻醉学院线350</t>
         </is>
@@ -3263,25 +3479,30 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>厦门</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n"/>
       <c r="F45" s="5" t="n"/>
       <c r="G45" s="5" t="n"/>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I45" s="5" t="n"/>
       <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L45" s="6" t="inlineStr">
+      <c r="M45" s="6" t="inlineStr">
         <is>
           <t>2025年录取3人均分336</t>
         </is>
@@ -3303,31 +3524,36 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n">
         <v>320</v>
       </c>
-      <c r="G46" s="5" t="n">
+      <c r="H46" s="5" t="n">
         <v>340</v>
       </c>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>50/50/160</t>
         </is>
       </c>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n">
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="L46" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L46" s="6" t="inlineStr">
+      <c r="M46" s="6" t="inlineStr">
         <is>
           <t>1051专硕校线；2026年齐鲁医院麻醉专硕均分392</t>
         </is>
@@ -3349,29 +3575,34 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="F47" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="G47" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="6" t="inlineStr">
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I47" s="5" t="n"/>
       <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L47" s="6" t="inlineStr">
+      <c r="M47" s="6" t="inlineStr">
         <is>
           <t>2025年录取28人均分344</t>
         </is>
@@ -3393,29 +3624,34 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>潍坊</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="F48" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="G48" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="6" t="inlineStr">
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I48" s="5" t="n"/>
       <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L48" s="6" t="inlineStr">
+      <c r="M48" s="6" t="inlineStr">
         <is>
           <t>2025年录取30人均分342</t>
         </is>
@@ -3437,29 +3673,34 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
+          <t>滨州</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="F49" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="G49" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I49" s="5" t="n"/>
       <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L49" s="6" t="inlineStr">
+      <c r="M49" s="6" t="inlineStr">
         <is>
           <t>2025年录取18人均分318，全国最低梯队</t>
         </is>
@@ -3481,29 +3722,34 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n">
+      <c r="F50" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="G50" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I50" s="5" t="n"/>
       <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L50" s="6" t="inlineStr">
+      <c r="M50" s="6" t="inlineStr">
         <is>
           <t>2025年录取22人均分352</t>
         </is>
@@ -3525,29 +3771,34 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>济宁</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n">
+      <c r="F51" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="G51" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I51" s="5" t="n"/>
       <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L51" s="6" t="inlineStr">
+      <c r="M51" s="6" t="inlineStr">
         <is>
           <t>2025年录取4人均分360</t>
         </is>
@@ -3569,33 +3820,38 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="F52" s="5" t="n">
         <v>315</v>
       </c>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n">
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n">
         <v>370</v>
       </c>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>55/55/190</t>
         </is>
       </c>
-      <c r="I52" s="5" t="n">
+      <c r="J52" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="J52" s="5" t="n">
+      <c r="K52" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="L52" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L52" s="6" t="inlineStr">
+      <c r="M52" s="6" t="inlineStr">
         <is>
           <t>2026年第一临床370、第二临床340、第三临床312</t>
         </is>
@@ -3617,27 +3873,32 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
+          <t>开封</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
           <t>双一流</t>
         </is>
       </c>
-      <c r="E53" s="5" t="n">
+      <c r="F53" s="5" t="n">
         <v>343</v>
       </c>
-      <c r="F53" s="5" t="n"/>
       <c r="G53" s="5" t="n"/>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I53" s="5" t="n"/>
       <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L53" s="6" t="inlineStr">
+      <c r="M53" s="6" t="inlineStr">
         <is>
           <t>2025年录取18人均分353</t>
         </is>
@@ -3659,25 +3920,30 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>新乡</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n"/>
       <c r="F54" s="5" t="n"/>
       <c r="G54" s="5" t="n"/>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I54" s="5" t="n"/>
       <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L54" s="6" t="inlineStr">
+      <c r="M54" s="6" t="inlineStr">
         <is>
           <t>麻醉学专业排名全国第33位</t>
         </is>
@@ -3699,25 +3965,30 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n"/>
       <c r="F55" s="5" t="n"/>
       <c r="G55" s="5" t="n"/>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I55" s="5" t="n"/>
       <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L55" s="6" t="inlineStr">
+      <c r="M55" s="6" t="inlineStr">
         <is>
           <t>2025年录取19人均分352</t>
         </is>
@@ -3739,25 +4010,30 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E56" s="5" t="n"/>
       <c r="F56" s="5" t="n"/>
       <c r="G56" s="5" t="n"/>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I56" s="5" t="n"/>
       <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L56" s="6" t="inlineStr">
+      <c r="M56" s="6" t="inlineStr">
         <is>
           <t>2025年录取8人均分362</t>
         </is>
@@ -3779,29 +4055,34 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
+          <t>十堰</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="F57" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F57" s="5" t="n">
+      <c r="G57" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I57" s="5" t="n"/>
       <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L57" s="6" t="inlineStr">
+      <c r="M57" s="6" t="inlineStr">
         <is>
           <t>2025年录取19人均分324</t>
         </is>
@@ -3823,29 +4104,34 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E58" s="5" t="n"/>
       <c r="F58" s="5" t="n"/>
-      <c r="G58" s="5" t="n">
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n">
         <v>310</v>
       </c>
-      <c r="H58" s="6" t="inlineStr">
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n">
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="L58" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L58" s="6" t="inlineStr">
+      <c r="M58" s="6" t="inlineStr">
         <is>
           <t>2025年录取24人均分374；2026年湘雅医院一志愿录取最低约386</t>
         </is>
@@ -3867,27 +4153,32 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="E59" s="5" t="n">
+      <c r="F59" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F59" s="5" t="n"/>
       <c r="G59" s="5" t="n"/>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I59" s="5" t="n"/>
       <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L59" s="6" t="inlineStr">
+      <c r="M59" s="6" t="inlineStr">
         <is>
           <t>2025年录取7人均分336</t>
         </is>
@@ -3909,25 +4200,30 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
+          <t>衡阳</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E60" s="5" t="n"/>
       <c r="F60" s="5" t="n"/>
       <c r="G60" s="5" t="n"/>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I60" s="5" t="n"/>
       <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L60" s="6" t="inlineStr">
+      <c r="M60" s="6" t="inlineStr">
         <is>
           <t>麻醉学专业排名全国第27位</t>
         </is>
@@ -3949,25 +4245,30 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="E61" s="5" t="n"/>
       <c r="F61" s="5" t="n"/>
       <c r="G61" s="5" t="n"/>
-      <c r="H61" s="6" t="inlineStr">
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I61" s="5" t="n"/>
       <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L61" s="6" t="inlineStr">
+      <c r="M61" s="6" t="inlineStr">
         <is>
           <t>2025年录取25人均分378，含省医临床学院均分402</t>
         </is>
@@ -3989,35 +4290,40 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E62" s="5" t="n">
+      <c r="F62" s="5" t="n">
         <v>315</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>310</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>310</v>
       </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="H62" s="5" t="n">
+        <v>310</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>45/45/170</t>
         </is>
       </c>
-      <c r="I62" s="5" t="n">
+      <c r="J62" s="5" t="n">
         <v>-5</v>
       </c>
-      <c r="J62" s="5" t="n">
+      <c r="K62" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="K62" s="5" t="inlineStr">
+      <c r="L62" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L62" s="6" t="inlineStr">
+      <c r="M62" s="6" t="inlineStr">
         <is>
           <t>2025年录取29人均分364；2026年各附属医院统一按310执行</t>
         </is>
@@ -4039,35 +4345,40 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="E63" s="5" t="n">
+      <c r="F63" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F63" s="5" t="n">
+      <c r="G63" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G63" s="5" t="n">
+      <c r="H63" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>36/36/108</t>
         </is>
       </c>
-      <c r="I63" s="5" t="n">
+      <c r="J63" s="5" t="n">
         <v>-10</v>
       </c>
-      <c r="J63" s="5" t="n">
+      <c r="K63" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="L63" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L63" s="6" t="inlineStr">
+      <c r="M63" s="6" t="inlineStr">
         <is>
           <t>2026年第三临床医学院294（复试比1:2）；2025年录取14人均分354</t>
         </is>
@@ -4089,25 +4400,30 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="E64" s="5" t="n"/>
       <c r="F64" s="5" t="n"/>
       <c r="G64" s="5" t="n"/>
-      <c r="H64" s="6" t="inlineStr">
+      <c r="H64" s="5" t="n"/>
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I64" s="5" t="n"/>
       <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="inlineStr">
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L64" s="6" t="inlineStr">
+      <c r="M64" s="6" t="inlineStr">
         <is>
           <t>2025年录取27人均分354</t>
         </is>
@@ -4129,29 +4445,34 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
+          <t>湛江</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E65" s="5" t="n">
+      <c r="F65" s="5" t="n">
         <v>317</v>
       </c>
-      <c r="F65" s="5" t="n">
+      <c r="G65" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G65" s="5" t="n"/>
-      <c r="H65" s="6" t="inlineStr">
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I65" s="5" t="n"/>
       <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L65" s="6" t="inlineStr">
+      <c r="M65" s="6" t="inlineStr">
         <is>
           <t>2025年录取31人均分354</t>
         </is>
@@ -4173,27 +4494,32 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
           <t>科研院所</t>
         </is>
       </c>
-      <c r="E66" s="5" t="n">
+      <c r="F66" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F66" s="5" t="n"/>
       <c r="G66" s="5" t="n"/>
-      <c r="H66" s="6" t="inlineStr">
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="6" t="inlineStr">
         <is>
           <t>42/50/170</t>
         </is>
       </c>
-      <c r="I66" s="5" t="n"/>
       <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="inlineStr">
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L66" s="6" t="inlineStr">
+      <c r="M66" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4215,25 +4541,30 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
+          <t>海口</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E67" s="5" t="n"/>
       <c r="F67" s="5" t="n"/>
       <c r="G67" s="5" t="n"/>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="H67" s="5" t="n"/>
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I67" s="5" t="n"/>
       <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L67" s="6" t="inlineStr">
+      <c r="M67" s="6" t="inlineStr">
         <is>
           <t>2025年录取9人均分353</t>
         </is>
@@ -4255,35 +4586,40 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E68" s="5" t="n">
+      <c r="F68" s="5" t="n">
         <v>360</v>
       </c>
-      <c r="F68" s="5" t="n">
+      <c r="G68" s="5" t="n">
         <v>355</v>
       </c>
-      <c r="G68" s="5" t="n">
+      <c r="H68" s="5" t="n">
         <v>370</v>
       </c>
-      <c r="H68" s="6" t="inlineStr">
+      <c r="I68" s="6" t="inlineStr">
         <is>
           <t>60/60/180</t>
         </is>
       </c>
-      <c r="I68" s="5" t="n">
+      <c r="J68" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J68" s="5" t="n">
+      <c r="K68" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="K68" s="5" t="inlineStr">
+      <c r="L68" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L68" s="6" t="inlineStr">
+      <c r="M68" s="6" t="inlineStr">
         <is>
           <t>2026年麻醉学拟录取最低371、最高438、录取8人；2025年录取7人均分372</t>
         </is>
@@ -4305,25 +4641,30 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E69" s="5" t="n"/>
       <c r="F69" s="5" t="n"/>
       <c r="G69" s="5" t="n"/>
-      <c r="H69" s="6" t="inlineStr">
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I69" s="5" t="n"/>
       <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="inlineStr">
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L69" s="6" t="inlineStr">
+      <c r="M69" s="6" t="inlineStr">
         <is>
           <t>2025年录取10人均分372</t>
         </is>
@@ -4345,29 +4686,34 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
+          <t>泸州</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="F70" s="5" t="n">
         <v>306</v>
       </c>
-      <c r="F70" s="5" t="n">
+      <c r="G70" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="6" t="inlineStr">
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I70" s="5" t="n"/>
       <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="inlineStr">
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L70" s="6" t="inlineStr">
+      <c r="M70" s="6" t="inlineStr">
         <is>
           <t>2025年录取26人均分371</t>
         </is>
@@ -4389,29 +4735,34 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
+          <t>南充</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E71" s="5" t="n">
+      <c r="F71" s="5" t="n">
         <v>335</v>
       </c>
-      <c r="F71" s="5" t="n">
+      <c r="G71" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="6" t="inlineStr">
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I71" s="5" t="n"/>
       <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L71" s="6" t="inlineStr">
+      <c r="M71" s="6" t="inlineStr">
         <is>
           <t>2026年录取30人均分358（区间295-399）</t>
         </is>
@@ -4433,27 +4784,32 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E72" s="5" t="n">
+      <c r="F72" s="5" t="n">
         <v>332</v>
       </c>
-      <c r="F72" s="5" t="n"/>
       <c r="G72" s="5" t="n"/>
-      <c r="H72" s="6" t="inlineStr">
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I72" s="5" t="n"/>
       <c r="J72" s="5" t="n"/>
-      <c r="K72" s="5" t="inlineStr">
+      <c r="K72" s="5" t="n"/>
+      <c r="L72" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L72" s="6" t="inlineStr">
+      <c r="M72" s="6" t="inlineStr">
         <is>
           <t>2024年拟录取14人最低332</t>
         </is>
@@ -4475,35 +4831,40 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="E73" s="5" t="n">
+      <c r="F73" s="5" t="n">
         <v>365</v>
       </c>
-      <c r="F73" s="5" t="n">
+      <c r="G73" s="5" t="n">
         <v>360</v>
       </c>
-      <c r="G73" s="5" t="n">
+      <c r="H73" s="5" t="n">
         <v>335</v>
       </c>
-      <c r="H73" s="6" t="inlineStr">
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I73" s="5" t="n">
+      <c r="J73" s="5" t="n">
         <v>-30</v>
       </c>
-      <c r="J73" s="5" t="n">
+      <c r="K73" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="K73" s="5" t="inlineStr">
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L73" s="6" t="inlineStr">
+      <c r="M73" s="6" t="inlineStr">
         <is>
           <t>2025年录取26人均分380，为西南最高；2026年降至335</t>
         </is>
@@ -4525,25 +4886,30 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
           <t>军队</t>
         </is>
       </c>
-      <c r="E74" s="5" t="n"/>
       <c r="F74" s="5" t="n"/>
       <c r="G74" s="5" t="n"/>
-      <c r="H74" s="6" t="inlineStr">
+      <c r="H74" s="5" t="n"/>
+      <c r="I74" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I74" s="5" t="n"/>
       <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="inlineStr">
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L74" s="6" t="inlineStr">
+      <c r="M74" s="6" t="inlineStr">
         <is>
           <t>2025年录取3人均分372</t>
         </is>
@@ -4565,35 +4931,40 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="F75" s="5" t="n">
         <v>319</v>
       </c>
-      <c r="F75" s="5" t="n">
+      <c r="G75" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G75" s="5" t="n">
+      <c r="H75" s="5" t="n">
         <v>319</v>
       </c>
-      <c r="H75" s="6" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>48/48/—</t>
         </is>
       </c>
-      <c r="I75" s="5" t="n">
+      <c r="J75" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J75" s="5" t="n">
+      <c r="K75" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="K75" s="5" t="inlineStr">
+      <c r="L75" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L75" s="6" t="inlineStr">
+      <c r="M75" s="6" t="inlineStr">
         <is>
           <t>2025年录取21人均分349；2026年疼痛方向录取6人均分338</t>
         </is>
@@ -4615,25 +4986,30 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
+          <t>遵义</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E76" s="5" t="n"/>
       <c r="F76" s="5" t="n"/>
       <c r="G76" s="5" t="n"/>
-      <c r="H76" s="6" t="inlineStr">
+      <c r="H76" s="5" t="n"/>
+      <c r="I76" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I76" s="5" t="n"/>
       <c r="J76" s="5" t="n"/>
-      <c r="K76" s="5" t="inlineStr">
+      <c r="K76" s="5" t="n"/>
+      <c r="L76" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L76" s="6" t="inlineStr">
+      <c r="M76" s="6" t="inlineStr">
         <is>
           <t>2025年录取24人均分343</t>
         </is>
@@ -4655,35 +5031,40 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E77" s="5" t="n">
+      <c r="F77" s="5" t="n">
         <v>325</v>
       </c>
-      <c r="F77" s="5" t="n">
+      <c r="G77" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G77" s="5" t="n">
+      <c r="H77" s="5" t="n">
         <v>315</v>
       </c>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="I77" s="6" t="inlineStr">
         <is>
           <t>45/45/99</t>
         </is>
       </c>
-      <c r="I77" s="5" t="n">
+      <c r="J77" s="5" t="n">
         <v>-10</v>
       </c>
-      <c r="J77" s="5" t="n">
+      <c r="K77" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="K77" s="5" t="inlineStr">
+      <c r="L77" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L77" s="6" t="inlineStr">
+      <c r="M77" s="6" t="inlineStr">
         <is>
           <t>2025年录取42人均分349</t>
         </is>
@@ -4705,29 +5086,34 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E78" s="5" t="n">
+      <c r="F78" s="5" t="n">
         <v>337</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="G78" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="G78" s="5" t="n"/>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="H78" s="5" t="n"/>
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I78" s="5" t="n"/>
       <c r="J78" s="5" t="n"/>
-      <c r="K78" s="5" t="inlineStr">
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L78" s="6" t="inlineStr">
+      <c r="M78" s="6" t="inlineStr">
         <is>
           <t>2025年录取4人均分325</t>
         </is>
@@ -4749,29 +5135,34 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
+          <t>大理</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
           <t>B区省属</t>
         </is>
       </c>
-      <c r="E79" s="5" t="n">
+      <c r="F79" s="5" t="n">
         <v>305</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="G79" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="G79" s="5" t="n"/>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="H79" s="5" t="n"/>
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I79" s="5" t="n"/>
       <c r="J79" s="5" t="n"/>
-      <c r="K79" s="5" t="inlineStr">
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="L79" s="6" t="inlineStr">
+      <c r="M79" s="6" t="inlineStr">
         <is>
           <t>2025年录取15人均分339</t>
         </is>
@@ -4793,29 +5184,34 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E80" s="5" t="n"/>
       <c r="F80" s="5" t="n"/>
-      <c r="G80" s="5" t="n">
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="n">
         <v>370</v>
       </c>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>60/60/200</t>
         </is>
       </c>
-      <c r="I80" s="5" t="n"/>
-      <c r="J80" s="5" t="n">
+      <c r="J80" s="5" t="n"/>
+      <c r="K80" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="K80" s="5" t="inlineStr">
+      <c r="L80" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L80" s="6" t="inlineStr">
+      <c r="M80" s="6" t="inlineStr">
         <is>
           <t>2026年校线330、麻醉学370，招生缩至6人；2025年录取10人均分374</t>
         </is>
@@ -4837,29 +5233,34 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E81" s="5" t="n">
+      <c r="F81" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="G81" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G81" s="5" t="n"/>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="H81" s="5" t="n"/>
+      <c r="I81" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I81" s="5" t="n"/>
       <c r="J81" s="5" t="n"/>
-      <c r="K81" s="5" t="inlineStr">
+      <c r="K81" s="5" t="n"/>
+      <c r="L81" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="L81" s="6" t="inlineStr">
+      <c r="M81" s="6" t="inlineStr">
         <is>
           <t>2025年录取18人均分341</t>
         </is>
@@ -4881,35 +5282,40 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
+          <t>延安</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E82" s="5" t="n">
+      <c r="F82" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F82" s="5" t="n">
+      <c r="G82" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="G82" s="5" t="n">
+      <c r="H82" s="5" t="n">
         <v>307</v>
       </c>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I82" s="5" t="n">
+      <c r="J82" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J82" s="5" t="n">
+      <c r="K82" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="K82" s="5" t="inlineStr">
+      <c r="L82" s="5" t="inlineStr">
         <is>
           <t>院自划线</t>
         </is>
       </c>
-      <c r="L82" s="6" t="inlineStr">
+      <c r="M82" s="6" t="inlineStr">
         <is>
           <t>2026年延安医学院麻醉学307分</t>
         </is>
@@ -4931,29 +5337,34 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
+          <t>咸阳</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E83" s="5" t="n">
+      <c r="F83" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="F83" s="5" t="n">
+      <c r="G83" s="5" t="n">
         <v>297</v>
       </c>
-      <c r="G83" s="5" t="n"/>
-      <c r="H83" s="6" t="inlineStr">
+      <c r="H83" s="5" t="n"/>
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I83" s="5" t="n"/>
       <c r="J83" s="5" t="n"/>
-      <c r="K83" s="5" t="inlineStr">
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="L83" s="6" t="inlineStr">
+      <c r="M83" s="6" t="inlineStr">
         <is>
           <t>2025年麻醉学专硕297分</t>
         </is>
@@ -4975,25 +5386,30 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="E84" s="5" t="n"/>
       <c r="F84" s="5" t="n"/>
       <c r="G84" s="5" t="n"/>
-      <c r="H84" s="6" t="inlineStr">
+      <c r="H84" s="5" t="n"/>
+      <c r="I84" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I84" s="5" t="n"/>
       <c r="J84" s="5" t="n"/>
-      <c r="K84" s="5" t="inlineStr">
+      <c r="K84" s="5" t="n"/>
+      <c r="L84" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L84" s="6" t="inlineStr">
+      <c r="M84" s="6" t="inlineStr">
         <is>
           <t>2025年录取16人均分354；2026年一临录取16人最低328</t>
         </is>
@@ -5015,29 +5431,34 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
           <t>B区省属</t>
         </is>
       </c>
-      <c r="E85" s="5" t="n">
+      <c r="F85" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="F85" s="5" t="n">
+      <c r="G85" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="G85" s="5" t="n"/>
-      <c r="H85" s="6" t="inlineStr">
+      <c r="H85" s="5" t="n"/>
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I85" s="5" t="n"/>
       <c r="J85" s="5" t="n"/>
-      <c r="K85" s="5" t="inlineStr">
+      <c r="K85" s="5" t="n"/>
+      <c r="L85" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="L85" s="6" t="inlineStr">
+      <c r="M85" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5059,27 +5480,32 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
           <t>B区省属</t>
         </is>
       </c>
-      <c r="E86" s="5" t="n">
+      <c r="F86" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="F86" s="5" t="n"/>
       <c r="G86" s="5" t="n"/>
-      <c r="H86" s="6" t="inlineStr">
+      <c r="H86" s="5" t="n"/>
+      <c r="I86" s="6" t="inlineStr">
         <is>
           <t>39/39/117</t>
         </is>
       </c>
-      <c r="I86" s="5" t="n"/>
       <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="inlineStr">
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="L86" s="6" t="inlineStr">
+      <c r="M86" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5101,29 +5527,34 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
           <t>B区省属</t>
         </is>
       </c>
-      <c r="E87" s="5" t="n">
+      <c r="F87" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="F87" s="5" t="n">
+      <c r="G87" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="G87" s="5" t="n"/>
-      <c r="H87" s="6" t="inlineStr">
+      <c r="H87" s="5" t="n"/>
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I87" s="5" t="n"/>
       <c r="J87" s="5" t="n"/>
-      <c r="K87" s="5" t="inlineStr">
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="L87" s="6" t="inlineStr">
+      <c r="M87" s="6" t="inlineStr">
         <is>
           <t>2025年录取20人均分342；2026年第三临床15人均分342</t>
         </is>
@@ -5145,25 +5576,30 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
+          <t>西宁</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
           <t>211/B区</t>
         </is>
       </c>
-      <c r="E88" s="5" t="n"/>
       <c r="F88" s="5" t="n"/>
       <c r="G88" s="5" t="n"/>
-      <c r="H88" s="6" t="inlineStr">
+      <c r="H88" s="5" t="n"/>
+      <c r="I88" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I88" s="5" t="n"/>
       <c r="J88" s="5" t="n"/>
-      <c r="K88" s="5" t="inlineStr">
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L88" s="6" t="inlineStr">
+      <c r="M88" s="6" t="inlineStr">
         <is>
           <t>2025年录取17人均分333</t>
         </is>
@@ -5185,29 +5621,34 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
+          <t>乌鲁木齐</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
           <t>B区省属</t>
         </is>
       </c>
-      <c r="E89" s="5" t="n">
+      <c r="F89" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="F89" s="5" t="n">
+      <c r="G89" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="G89" s="5" t="n"/>
-      <c r="H89" s="6" t="inlineStr">
+      <c r="H89" s="5" t="n"/>
+      <c r="I89" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I89" s="5" t="n"/>
       <c r="J89" s="5" t="n"/>
-      <c r="K89" s="5" t="inlineStr">
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="L89" s="6" t="inlineStr">
+      <c r="M89" s="6" t="inlineStr">
         <is>
           <t>2025年录取62人均分324；2026年一临31人均分325</t>
         </is>
@@ -5229,25 +5670,30 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
+          <t>石河子</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
           <t>211/B区</t>
         </is>
       </c>
-      <c r="E90" s="5" t="n"/>
       <c r="F90" s="5" t="n"/>
       <c r="G90" s="5" t="n"/>
-      <c r="H90" s="6" t="inlineStr">
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I90" s="5" t="n"/>
       <c r="J90" s="5" t="n"/>
-      <c r="K90" s="5" t="inlineStr">
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L90" s="6" t="inlineStr">
+      <c r="M90" s="6" t="inlineStr">
         <is>
           <t>2025年录取3人均分320</t>
         </is>
@@ -5269,29 +5715,34 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
+          <t>拉萨</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
           <t>211/B区</t>
         </is>
       </c>
-      <c r="E91" s="5" t="n">
+      <c r="F91" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="F91" s="5" t="n">
+      <c r="G91" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="G91" s="5" t="n"/>
-      <c r="H91" s="6" t="inlineStr">
+      <c r="H91" s="5" t="n"/>
+      <c r="I91" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I91" s="5" t="n"/>
       <c r="J91" s="5" t="n"/>
-      <c r="K91" s="5" t="inlineStr">
+      <c r="K91" s="5" t="n"/>
+      <c r="L91" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="L91" s="6" t="inlineStr">
+      <c r="M91" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5313,27 +5764,32 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
+          <t>百色</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
           <t>B区省属</t>
         </is>
       </c>
-      <c r="E92" s="5" t="n">
+      <c r="F92" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="F92" s="5" t="n"/>
       <c r="G92" s="5" t="n"/>
-      <c r="H92" s="6" t="inlineStr">
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="6" t="inlineStr">
         <is>
           <t>39/39/117</t>
         </is>
       </c>
-      <c r="I92" s="5" t="n"/>
       <c r="J92" s="5" t="n"/>
-      <c r="K92" s="5" t="inlineStr">
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="L92" s="6" t="inlineStr">
+      <c r="M92" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5355,36 +5811,41 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
+          <t>南宁</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="E93" s="5" t="n"/>
       <c r="F93" s="5" t="n"/>
       <c r="G93" s="5" t="n"/>
-      <c r="H93" s="6" t="inlineStr">
+      <c r="H93" s="5" t="n"/>
+      <c r="I93" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I93" s="5" t="n"/>
       <c r="J93" s="5" t="n"/>
-      <c r="K93" s="5" t="inlineStr">
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L93" s="6" t="inlineStr">
+      <c r="M93" s="6" t="inlineStr">
         <is>
           <t>麻醉学专业排名全国第16位</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L93"/>
+  <autoFilter ref="A2:M93"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="J3:J93">
+  <conditionalFormatting sqref="K3:K93">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>60</formula>
     </cfRule>
@@ -5396,7 +5857,7 @@
       <formula>30</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I93">
+  <conditionalFormatting sqref="J3:J93">
     <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -11694,18 +12155,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -11733,30 +12195,35 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
           <t>2024复试线</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>政治</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>外语</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>专业课(306)</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>线类型</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -11776,24 +12243,29 @@
           <t>重庆</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
         <v>365</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>50</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G3" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>当年西南最高</t>
         </is>
@@ -11813,24 +12285,29 @@
           <t>四川</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>360</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>60</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>60</v>
       </c>
       <c r="G4" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>1051临床医学专硕校线</t>
         </is>
@@ -11850,24 +12327,29 @@
           <t>江苏</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>347</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G5" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>首次大规模招生10人</t>
         </is>
@@ -11887,24 +12369,29 @@
           <t>浙江</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>温州</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>345</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>录取9人最低349最高420均分373</t>
         </is>
@@ -11924,24 +12411,29 @@
           <t>天津</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
         <v>344</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>55</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>55</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>录取9人，2025年涨至361</t>
         </is>
@@ -11961,24 +12453,29 @@
           <t>山西</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>343</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>首次招生</t>
         </is>
@@ -11998,24 +12495,29 @@
           <t>河南</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>开封</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
         <v>343</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12035,24 +12537,29 @@
           <t>北京</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>340</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>50</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>190</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>一志愿拟录取16人最低342</t>
         </is>
@@ -12072,24 +12579,29 @@
           <t>云南</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
         <v>337</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>39</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G11" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12109,24 +12621,29 @@
           <t>四川</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>南充</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>335</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G12" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12146,24 +12663,29 @@
           <t>四川</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
         <v>332</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G13" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>拟录取14人最低332</t>
         </is>
@@ -12183,24 +12705,29 @@
           <t>江苏</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>镇江</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>327</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>60</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>60</v>
       </c>
       <c r="G14" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>190</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>单科要求较高</t>
         </is>
@@ -12220,24 +12747,29 @@
           <t>云南</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
         <v>325</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>45</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>45</v>
       </c>
       <c r="G15" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12257,24 +12789,29 @@
           <t>湖南</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>吉首</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>323</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>39</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12294,24 +12831,29 @@
           <t>江苏</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>无锡</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
         <v>319</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12331,24 +12873,29 @@
           <t>贵州</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
         <v>319</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>54</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>54</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>单科要求最高之一</t>
         </is>
@@ -12368,24 +12915,29 @@
           <t>广东</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>湛江</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n">
         <v>317</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>50</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G19" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12405,24 +12957,29 @@
           <t>浙江</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>绍兴</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>317</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G20" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>录取6人均分334.8</t>
         </is>
@@ -12442,24 +12999,29 @@
           <t>吉林</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
         <v>316</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G21" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H21" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12479,24 +13041,29 @@
           <t>河南</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>315</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>50</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G22" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H22" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>2026年一临已涨至370</t>
         </is>
@@ -12516,24 +13083,29 @@
           <t>福建</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
         <v>315</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>50</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G23" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>2026年涨至350</t>
         </is>
@@ -12553,24 +13125,29 @@
           <t>广东</t>
         </is>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
         <v>315</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>50</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G24" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H24" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>三年稳定在310-315</t>
         </is>
@@ -12590,24 +13167,29 @@
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
         <v>310</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>50</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G25" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>校线(1051)</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>麻醉学调剂录取分383-389</t>
         </is>
@@ -12627,24 +13209,29 @@
           <t>辽宁</t>
         </is>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
         <v>310</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>50</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G26" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H26" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>校线</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>2025年降至305</t>
         </is>
@@ -12664,24 +13251,29 @@
           <t>江苏</t>
         </is>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>扬州</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
         <v>310</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G27" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H27" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="J27" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12701,24 +13293,29 @@
           <t>江苏</t>
         </is>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
         <v>308</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G28" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H28" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12738,24 +13335,29 @@
           <t>四川</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>泸州</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
         <v>306</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G29" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H29" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12775,24 +13377,29 @@
           <t>云南</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>大理</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
         <v>305</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>39</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G30" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H30" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>院线</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12812,24 +13419,29 @@
           <t>江苏</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>徐州</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G31" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H31" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>2025年342、2026年332</t>
         </is>
@@ -12849,24 +13461,29 @@
           <t>安徽</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G32" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H32" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="J32" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12886,24 +13503,29 @@
           <t>山东</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G33" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H33" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="J33" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12923,24 +13545,29 @@
           <t>山东</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>潍坊</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G34" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H34" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="J34" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12960,24 +13587,29 @@
           <t>山东</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>济宁</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G35" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H35" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="J35" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12997,24 +13629,29 @@
           <t>河北</t>
         </is>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G36" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H36" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="J36" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13034,24 +13671,29 @@
           <t>河北</t>
         </is>
       </c>
-      <c r="D37" s="5" t="n">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>保定</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G37" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H37" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="J37" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13071,24 +13713,29 @@
           <t>辽宁</t>
         </is>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>锦州</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G38" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H38" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13108,24 +13755,29 @@
           <t>辽宁</t>
         </is>
       </c>
-      <c r="D39" s="5" t="n">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G39" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H39" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="J39" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13145,24 +13797,29 @@
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n">
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G40" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H40" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>现更名牡丹江医科大学</t>
         </is>
@@ -13182,24 +13839,29 @@
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="D41" s="5" t="n">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>齐齐哈尔</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F41" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G41" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H41" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="J41" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13219,24 +13881,29 @@
           <t>湖北</t>
         </is>
       </c>
-      <c r="D42" s="5" t="n">
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>十堰</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G42" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H42" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13256,24 +13923,29 @@
           <t>湖北</t>
         </is>
       </c>
-      <c r="D43" s="5" t="n">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F43" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G43" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H43" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
+      <c r="J43" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13293,24 +13965,29 @@
           <t>湖北</t>
         </is>
       </c>
-      <c r="D44" s="5" t="n">
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>荆州</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G44" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H44" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="J44" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13330,24 +14007,29 @@
           <t>湖南</t>
         </is>
       </c>
-      <c r="D45" s="5" t="n">
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F45" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G45" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H45" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="J45" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13367,24 +14049,29 @@
           <t>江西</t>
         </is>
       </c>
-      <c r="D46" s="5" t="n">
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G46" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H46" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="J46" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13404,24 +14091,29 @@
           <t>江西</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n">
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>赣州</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F47" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H47" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I47" s="6" t="inlineStr">
+      <c r="J47" s="6" t="inlineStr">
         <is>
           <t>现更名赣南医科大学</t>
         </is>
@@ -13441,24 +14133,29 @@
           <t>安徽</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n">
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>芜湖</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G48" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H48" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
+      <c r="J48" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13478,24 +14175,29 @@
           <t>安徽</t>
         </is>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>蚌埠</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F49" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G49" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H49" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="J49" s="6" t="inlineStr">
         <is>
           <t>现更名蚌埠医科大学</t>
         </is>
@@ -13515,24 +14217,29 @@
           <t>广东</t>
         </is>
       </c>
-      <c r="D50" s="5" t="n">
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G50" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H50" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="J50" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13552,24 +14259,29 @@
           <t>浙江</t>
         </is>
       </c>
-      <c r="D51" s="5" t="n">
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F51" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G51" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H51" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="J51" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13589,24 +14301,29 @@
           <t>浙江</t>
         </is>
       </c>
-      <c r="D52" s="5" t="n">
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G52" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H52" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="J52" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13626,24 +14343,29 @@
           <t>浙江</t>
         </is>
       </c>
-      <c r="D53" s="5" t="n">
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>湖州</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F53" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G53" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H53" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="J53" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13663,24 +14385,29 @@
           <t>四川</t>
         </is>
       </c>
-      <c r="D54" s="5" t="n">
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G54" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H54" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="J54" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13700,24 +14427,29 @@
           <t>山西</t>
         </is>
       </c>
-      <c r="D55" s="5" t="n">
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>长治</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F55" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G55" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H55" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="J55" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13737,24 +14469,29 @@
           <t>陕西</t>
         </is>
       </c>
-      <c r="D56" s="5" t="n">
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G56" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H56" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
+      <c r="J56" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13774,24 +14511,29 @@
           <t>广东</t>
         </is>
       </c>
-      <c r="D57" s="5" t="n">
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="E57" s="5" t="n">
+      <c r="F57" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="F57" s="5" t="n">
+      <c r="G57" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="G57" s="5" t="n">
+      <c r="H57" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="J57" s="6" t="inlineStr">
         <is>
           <t>科研院所</t>
         </is>
@@ -13811,24 +14553,29 @@
           <t>北京</t>
         </is>
       </c>
-      <c r="D58" s="5" t="n">
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
         <v>304</v>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>42</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>42</v>
       </c>
       <c r="G58" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H58" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>国家A线</t>
         </is>
       </c>
-      <c r="I58" s="6" t="inlineStr">
+      <c r="J58" s="6" t="inlineStr">
         <is>
           <t>军队院校</t>
         </is>
@@ -13848,24 +14595,29 @@
           <t>宁夏</t>
         </is>
       </c>
-      <c r="D59" s="5" t="n">
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
         <v>294</v>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>39</v>
       </c>
       <c r="F59" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G59" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H59" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr">
+      <c r="J59" s="6" t="inlineStr">
         <is>
           <t>B区</t>
         </is>
@@ -13885,24 +14637,29 @@
           <t>西藏</t>
         </is>
       </c>
-      <c r="D60" s="5" t="n">
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>拉萨</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
         <v>294</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>39</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G60" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H60" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr">
+      <c r="J60" s="6" t="inlineStr">
         <is>
           <t>B区</t>
         </is>
@@ -13922,24 +14679,29 @@
           <t>吉林</t>
         </is>
       </c>
-      <c r="D61" s="5" t="n">
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>延吉</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
         <v>294</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>39</v>
       </c>
       <c r="F61" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G61" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H61" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="I61" s="6" t="inlineStr">
+      <c r="J61" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13959,24 +14721,29 @@
           <t>内蒙古</t>
         </is>
       </c>
-      <c r="D62" s="5" t="n">
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
         <v>294</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>39</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G62" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H62" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
+      <c r="J62" s="6" t="inlineStr">
         <is>
           <t>B区</t>
         </is>
@@ -13996,24 +14763,29 @@
           <t>内蒙古</t>
         </is>
       </c>
-      <c r="D63" s="5" t="n">
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>包头</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
         <v>294</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>39</v>
       </c>
       <c r="F63" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G63" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H63" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="I63" s="6" t="inlineStr">
+      <c r="J63" s="6" t="inlineStr">
         <is>
           <t>B区</t>
         </is>
@@ -14033,24 +14805,29 @@
           <t>内蒙古</t>
         </is>
       </c>
-      <c r="D64" s="5" t="n">
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>通辽</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
         <v>294</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>39</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G64" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H64" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="I64" s="6" t="inlineStr">
+      <c r="J64" s="6" t="inlineStr">
         <is>
           <t>B区</t>
         </is>
@@ -14070,24 +14847,29 @@
           <t>甘肃</t>
         </is>
       </c>
-      <c r="D65" s="5" t="n">
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
         <v>294</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>39</v>
       </c>
       <c r="F65" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G65" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H65" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
+      <c r="J65" s="6" t="inlineStr">
         <is>
           <t>B区</t>
         </is>
@@ -14107,24 +14889,29 @@
           <t>甘肃</t>
         </is>
       </c>
-      <c r="D66" s="5" t="n">
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
         <v>294</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>39</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G66" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H66" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="I66" s="6" t="inlineStr">
+      <c r="J66" s="6" t="inlineStr">
         <is>
           <t>B区</t>
         </is>
@@ -14144,24 +14931,29 @@
           <t>新疆</t>
         </is>
       </c>
-      <c r="D67" s="5" t="n">
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>乌鲁木齐</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
         <v>294</v>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>39</v>
       </c>
       <c r="F67" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G67" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H67" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="J67" s="6" t="inlineStr">
         <is>
           <t>B区</t>
         </is>
@@ -14181,31 +14973,36 @@
           <t>广西</t>
         </is>
       </c>
-      <c r="D68" s="5" t="n">
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>百色</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
         <v>294</v>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>39</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>39</v>
       </c>
       <c r="G68" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H68" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>国家B线</t>
         </is>
       </c>
-      <c r="I68" s="6" t="inlineStr">
+      <c r="J68" s="6" t="inlineStr">
         <is>
           <t>B区</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I68"/>
+  <autoFilter ref="A2:J68"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -14220,15 +15017,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -14261,10 +15059,15 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>所在城市</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
           <t>院校层次</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>备注 / 麻醉学科实力</t>
         </is>
@@ -14291,10 +15094,15 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>985/双一流</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>湘雅医学院；麻醉学科1956年成立，国家临床重点专科最多之一</t>
         </is>
@@ -14321,10 +15129,15 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>985/双一流</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>同济医学院；2022年软科曾位列全国第1</t>
         </is>
@@ -14351,10 +15164,15 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>211/双一流</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>国家级一流本科专业；2025年获批国家临床重点专科</t>
         </is>
@@ -14381,10 +15199,15 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>原第一军医大学；2025年录取25人均分378</t>
         </is>
@@ -14411,10 +15234,15 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>钟南山团队所在校；2025年录取27人均分354</t>
         </is>
@@ -14441,10 +15269,15 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>红医摇篮；2025年录取42人均分363</t>
         </is>
@@ -14471,10 +15304,15 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>2025年录取46人均分363，招生规模大</t>
         </is>
@@ -14501,10 +15339,15 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>2025年录取26人均分380，西南最高</t>
         </is>
@@ -14531,10 +15374,15 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>徐州</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>创办中国第一个麻醉学本科专业；校友会2023-2026连续四年A++、全国第1</t>
         </is>
@@ -14561,10 +15409,15 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>211/双一流</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>2026年一临麻醉学复试线370</t>
         </is>
@@ -14591,10 +15444,15 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>2025年录取47人均分360</t>
         </is>
@@ -14621,10 +15479,15 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>温州</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>2025年录取47人均分351</t>
         </is>
@@ -14651,10 +15514,15 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>211/双一流</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>2025年录取61人，招生规模全国前列</t>
         </is>
@@ -14681,10 +15549,15 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>2026年院线提至350</t>
         </is>
@@ -14711,10 +15584,15 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>大连</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>2025年录取48人均分340</t>
         </is>
@@ -14741,10 +15619,15 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>南宁</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -14771,10 +15654,15 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>2025年录取44人均分362</t>
         </is>
@@ -14801,10 +15689,15 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>985/双一流</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>2026年一临录取16人最低328</t>
         </is>
@@ -14831,10 +15724,15 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>泸州</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>2025年录取26人均分371</t>
         </is>
@@ -14861,10 +15759,15 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>2025年录取42人均分349</t>
         </is>
@@ -14891,10 +15794,15 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>省属重点</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>2025年录取31人均分351</t>
         </is>
@@ -14921,10 +15829,15 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>湛江</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>2025年录取31人均分354</t>
         </is>
@@ -14951,10 +15864,15 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>遵义</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>2025年录取24人均分343</t>
         </is>
@@ -14981,10 +15899,15 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>潍坊</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>原潍坊医学院；2025年录取30人均分342</t>
         </is>
@@ -15011,10 +15934,15 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>B区省属</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>2025年录取20人均分342，性价比高</t>
         </is>
@@ -15041,10 +15969,15 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>乌鲁木齐</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>B区省属</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>2025年录取62人，招生规模全国最大</t>
         </is>
@@ -15071,10 +16004,15 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>衡阳</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -15101,10 +16039,15 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>2025年录取21人均分349；2026疼痛方向均分338</t>
         </is>
@@ -15131,10 +16074,15 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
+          <t>滨州</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>2025年录取18人均分318，全国最低梯队</t>
         </is>
@@ -15161,10 +16109,15 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
+          <t>十堰</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>2025年录取19人均分324</t>
         </is>
@@ -15191,10 +16144,15 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>2025年录取28人均分344</t>
         </is>
@@ -15221,10 +16179,15 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
+          <t>蚌埠</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>2025年录取29人均分349；2026年14人均分330</t>
         </is>
@@ -15251,19 +16214,24 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
+          <t>新乡</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F35"/>
+  <autoFilter ref="A2:G35"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:C35">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="5">
@@ -15280,7 +16248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15339,281 +16307,294 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr"/>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>院校所在地</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>「地区」列为院校所属省级行政区，「城市」列为院校所在（主校区/研究生培养）地级市。直辖市地区与城市同名；中国香港/中国澳门/中国台湾未收录。个别院校多校区办学（如滨州医学院在烟台、滨州两地），城市列取考研院校代码库口径的主校区城市，实际培养校区请以当年招生简章为准。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>二、三年国家线（临床医学类专硕，与医学门类同线）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>2024 年</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>A 区 304 分（单科 42 / 126）；B 区 294 分（单科 39 / 117）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>2025 年</t>
+          <t>2024 年</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>A 区 293 分（单科 36 / 108）；B 区 283 分（单科 33 / 99）</t>
+          <t>A 区 304 分（单科 42 / 126）；B 区 294 分（单科 39 / 117）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
+          <t>2025 年</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>A 区 293 分（单科 36 / 108）；B 区 283 分（单科 33 / 99）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
           <t>2026 年</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>A 区 294 分（单科 36 / 108）；B 区 284 分（单科 33 / 99）</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>三、表内「复试线」与「录取分」的区别（关键）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>复试线</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>进入复试的最低初试总分门槛，由院校/学院自行划定，差额比例一般不低于 1:1.2，部分院校达 1:2。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>录取最低分 / 平均分</t>
+          <t>复试线</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>实际拟录取考生的初试分数，通常显著高于复试线（头部院校可高 30~60 分）。择校时应以录取分为主要参考。</t>
+          <t>进入复试的最低初试总分门槛，由院校/学院自行划定，差额比例一般不低于 1:1.2，部分院校达 1:2。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
+          <t>录取最低分 / 平均分</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>实际拟录取考生的初试分数，通常显著高于复试线（头部院校可高 30~60 分）。择校时应以录取分为主要参考。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
           <t>校线 vs 院线</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>「校线」为学校对 1051 一级学科的划线（如复旦 320、交大 330、首都医科 330）；「院线」为具体学院/基地按生源单独划的线（如郑州大学第一临床医学院 370）。表内已用「数据性质」列区分。</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>四、数据来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>官方来源</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>各院校研究生院/研究生招生网公布的复试分数线公告、拟录取名单、招生专业目录（如四川大学 yz.scu.edu.cn、上海交通大学 yzb.sjtu.edu.cn、福建医科大学 yjsy.fjmu.edu.cn、江苏大学 yz.ujs.edu.cn、中南大学湘雅医院、首都医科大学、徐州医科大学等）。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>教育部/研招网</t>
+          <t>官方来源</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>全国硕士研究生招生考试考生进入复试的初试成绩基本要求（2024/2025/2026 年，yz.chsi.com.cn）。</t>
+          <t>各院校研究生院/研究生招生网公布的复试分数线公告、拟录取名单、招生专业目录（如四川大学 yz.scu.edu.cn、上海交通大学 yzb.sjtu.edu.cn、福建医科大学 yjsy.fjmu.edu.cn、江苏大学 yz.ujs.edu.cn、中南大学湘雅医院、首都医科大学、徐州医科大学等）。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>第三方整理</t>
+          <t>教育部/研招网</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>启航考研、中公考研、新东方在线、路灯考研、掌上考研、宏医教育等平台按官网数据整理的院校分数线与报录比汇总表；2025 年录取明细（录取人数/最高/最低/平均分）来自医学考研类公众号对 90+ 培养单位拟录取名单的不完全统计。</t>
+          <t>全国硕士研究生招生考试考生进入复试的初试成绩基本要求（2024/2025/2026 年，yz.chsi.com.cn）。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>第三方整理</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>启航考研、中公考研、新东方在线、路灯考研、掌上考研、宏医教育等平台按官网数据整理的院校分数线与报录比汇总表；2025 年录取明细（录取人数/最高/最低/平均分）来自医学考研类公众号对 90+ 培养单位拟录取名单的不完全统计。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
           <t>排名来源</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>软科 2025 中国大学专业排名（麻醉学，33 所上榜）、校友会 2025 中国大学一流专业排名（研究型）。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr"/>
-    </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>五、使用须知与免责</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>数据时效</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>覆盖 2024、2025、2026 三个考研年度（分别对应 2023 年 12 月、2024 年 12 月、2025 年 12 月初试）。2026 年部分院校尚未公布复试线或拟录取数据，表中以空白表示。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>统计口径差异</t>
+          <t>数据时效</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>部分院校按 1051 一级学科统一划线，未单列 105118，表内已标注「校线」；部分院校按附属医院/临床学院分别划线，已尽可能拆分到培养单位层级。</t>
+          <t>覆盖 2024、2025、2026 三个考研年度（分别对应 2023 年 12 月、2024 年 12 月、2025 年 12 月初试）。2026 年部分院校尚未公布复试线或拟录取数据，表中以空白表示。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>可能存在误差</t>
+          <t>统计口径差异</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>第三方整理数据存在少量错漏（如个别培养单位录取人数或最高分缺失、个别年份分数线口径不一致），报考前请务必以目标院校研究生院官网最新公告为唯一依据。</t>
+          <t>部分院校按 1051 一级学科统一划线，未单列 105118，表内已标注「校线」；部分院校按附属医院/临床学院分别划线，已尽可能拆分到培养单位层级。</t>
         </is>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
+          <t>可能存在误差</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>第三方整理数据存在少量错漏（如个别培养单位录取人数或最高分缺失、个别年份分数线口径不一致），报考前请务必以目标院校研究生院官网最新公告为唯一依据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
           <t>建议用法</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>① 先用「三年复试线对比」筛选分数区间与目标层次；② 再用「2025录取明细」核对目标培养单位的实际录取分与招生规模；③ 结合「麻醉学专业排名」判断学科实力；④ 以「2026复试线明细」确认最新门槛。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>六、制表说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="42" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>生成日期</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
+          <t>生成日期</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>总览看板 / 三年复试线对比 / 2026复试线明细 / 2025录取明细 / 2024复试线明细 / 麻醉学专业排名 / 数据来源与说明</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A23:D23"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A30:D30"/>
-    <mergeCell ref="B9:D9"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/105118麻醉学考研三年数据统计表.xlsx
+++ b/105118麻醉学考研三年数据统计表.xlsx
@@ -16,10 +16,10 @@
     <sheet name="数据来源与说明" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'三年复试线对比'!$A$2:$M$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2026复试线明细'!$A$2:$F$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2025录取明细'!$A$2:$I$153</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2024复试线明细'!$A$2:$J$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'三年复试线对比'!$A$2:$P$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2026复试线明细'!$A$2:$G$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2025录取明细'!$A$2:$I$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2024复试线明细'!$A$2:$J$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'麻醉学专业排名'!$A$2:$G$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,13 @@
     <font>
       <name val="微软雅黑"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -122,18 +129,19 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -151,21 +159,25 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -754,7 +766,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -762,7 +774,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -770,7 +782,7 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
@@ -780,7 +792,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -788,7 +800,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -796,7 +808,7 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>352.3</v>
+        <v>352.2</v>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
@@ -1050,13 +1062,13 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>354.1</v>
+        <v>353.7</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>295</v>
@@ -1170,13 +1182,13 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>352.3</v>
+        <v>352.2</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>283</v>
@@ -1235,7 +1247,7 @@
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>7. 招生规模提示：2025 年不完全统计全国麻醉学专硕录取 1600+ 人，招生大户为新疆医科大学（62 人）、南昌大学（61 人）、大连医科大学（48 人）、温州医科大学（47 人）、哈尔滨医科大学（46 人）。</t>
+          <t>7. 招生规模提示：2025 年不完全统计全国麻醉学专硕录取 1600+ 人；温州医科大学官方统计中105118分培养单位合计49人（第一临床21、第二临床19、研究生培养基地8、台州医院1）。</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1287,8 +1299,11 @@
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
     <col width="52" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1364,6 +1379,21 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>2024官方来源</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>2025官方来源</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>2026官方来源</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -1413,6 +1443,9 @@
           <t>医学门类专硕校线，麻醉学按1051执行；实际录取分远高于校线</t>
         </is>
       </c>
+      <c r="N3" s="6" t="n"/>
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -1462,6 +1495,9 @@
           <t>2026年统考计划7人</t>
         </is>
       </c>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -1517,6 +1553,9 @@
           <t>2024年拟录取16人最低342；2025年录取12人均分358；2026统考可招约10人</t>
         </is>
       </c>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -1566,6 +1605,9 @@
           <t>2025年专硕361分；2026年计划扩至17人（2025年10人）</t>
         </is>
       </c>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -1607,12 +1649,27 @@
       <c r="K7" s="5" t="n"/>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
           <t>2025年录取44人均分362</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -1660,6 +1717,9 @@
           <t>2025年录取约10人均分335（循国家A线）</t>
         </is>
       </c>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -1709,6 +1769,9 @@
           <t>2024年首次招生343；2025年录取31人均分351</t>
         </is>
       </c>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -1758,6 +1821,9 @@
           <t>2025年麻醉学自划线304，高于当年国家线11分</t>
         </is>
       </c>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -1799,12 +1865,27 @@
       <c r="K11" s="5" t="n"/>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
           <t>2025年录取43人均分335；2026年一临录取5人均分330</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -1862,6 +1943,9 @@
           <t>2026年为1051校线；2025年录取42人均分363；306单科要求170分</t>
         </is>
       </c>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -1903,12 +1987,27 @@
       <c r="K13" s="5" t="n"/>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
           <t>2025年录取48人均分340</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P13" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -1952,12 +2051,27 @@
       <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
           <t>2025年录取42人均分332</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P14" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2115,27 @@
       <c r="K15" s="5" t="n"/>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P15" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -2056,6 +2185,9 @@
           <t>2024年麻醉学调剂录取分383-389，调剂门槛极高</t>
         </is>
       </c>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -2101,6 +2233,9 @@
           <t>2025年录取约9人均分356（原表数据不完整）</t>
         </is>
       </c>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -2142,12 +2277,27 @@
       <c r="K18" s="5" t="n"/>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
           <t>2025年录取5人均分354</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O18" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P18" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -2205,6 +2355,9 @@
           <t>2026年麻醉学（附属红旗医院基地）322分</t>
         </is>
       </c>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -2254,6 +2407,9 @@
           <t>2025年录取28人均分375</t>
         </is>
       </c>
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -2279,9 +2435,7 @@
           <t>211</t>
         </is>
       </c>
-      <c r="F21" s="5" t="n">
-        <v>294</v>
-      </c>
+      <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="6" t="inlineStr">
@@ -2293,14 +2447,17 @@
       <c r="K21" s="5" t="n"/>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>校线</t>
+          <t>待核验</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>2025年录取37人均分336</t>
-        </is>
-      </c>
+          <t>旧表误把吉林院校标作B区线，已撤销294；2025年录取37人均分336</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="n"/>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -2350,6 +2507,9 @@
           <t>1051专硕校线；麻醉统招约8人，实际录取远高于校线</t>
         </is>
       </c>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -2399,6 +2559,9 @@
           <t>1051专硕校线；2025年瑞金医院麻醉录取1人352</t>
         </is>
       </c>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -2448,6 +2611,9 @@
           <t>2025年专硕录取13人；2026年专硕计划13人</t>
         </is>
       </c>
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -2493,6 +2659,9 @@
           <t>2025年录取1人353分</t>
         </is>
       </c>
+      <c r="N25" s="6" t="n"/>
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -2542,6 +2711,9 @@
           <t>2024年录取10人；2025年专硕录取6人，线降29分</t>
         </is>
       </c>
+      <c r="N26" s="6" t="n"/>
+      <c r="O26" s="6" t="n"/>
+      <c r="P26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -2591,6 +2763,9 @@
           <t>2026年第一临床367、四临（肿瘤337/妇产354）；2025年录取34人均分365</t>
         </is>
       </c>
+      <c r="N27" s="6" t="n"/>
+      <c r="O27" s="6" t="n"/>
+      <c r="P27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -2638,12 +2813,27 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>校方执行A/B区线</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
           <t>2026年招生7人；2025年录取8人均分345</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>https://yz.ujs.edu.cn/info/1014/6087.htm</t>
+        </is>
+      </c>
+      <c r="O28" s="10" t="inlineStr">
+        <is>
+          <t>https://yz.ujs.edu.cn/info/1014/7517.htm</t>
+        </is>
+      </c>
+      <c r="P28" s="10" t="inlineStr">
+        <is>
+          <t>https://yz.ujs.edu.cn/info/1014/8467.htm</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2865,7 @@
         <v>319</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>335</v>
@@ -2698,7 +2888,22 @@
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>2026年无锡医学院335；2025年录取9人均分337</t>
+          <t>105118复试线：2024年319、2025年310、2026年335；2025年录取9人均分337</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>https://yz.jiangnan.edu.cn/info/1075/3414.htm</t>
+        </is>
+      </c>
+      <c r="O29" s="10" t="inlineStr">
+        <is>
+          <t>https://yz.jiangnan.edu.cn/info/1075/3574.htm</t>
+        </is>
+      </c>
+      <c r="P29" s="10" t="inlineStr">
+        <is>
+          <t>https://yz.jiangnan.edu.cn/info/1029/3750.htm</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2947,27 @@
       <c r="K30" s="5" t="n"/>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
           <t>2025年录取19人均分341</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O30" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P30" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -2797,12 +3017,27 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
           <t>2025年录取8人均分333</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O31" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P31" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -2831,7 +3066,7 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>342</v>
@@ -2845,21 +3080,32 @@
         </is>
       </c>
       <c r="J32" s="5" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>38</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>院线</t>
+          <t>院线（麻醉学院）</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>麻醉学院332；2026年盐城临床362/淮安358/连云港352；麻醉学全国第一</t>
-        </is>
-      </c>
+          <t>代表口径为麻醉学院：2024年321、2025年342、2026年332；其他培养单位另见年度明细</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>https://yjs.xzhmu.edu.cn/__local/A/DE/15/B317261DCA3748545A834BC395A_E639B01C_18527.pdf</t>
+        </is>
+      </c>
+      <c r="O32" s="10" t="inlineStr">
+        <is>
+          <t>https://yjs.xzhmu.edu.cn/__local/B/0A/48/EB59205400D767FDD031BF33A0F_BD607B42_24B06.pdf</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -2905,6 +3151,9 @@
           <t>2025年录取6人均分383，为全国最高梯队</t>
         </is>
       </c>
+      <c r="N33" s="6" t="n"/>
+      <c r="O33" s="6" t="n"/>
+      <c r="P33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -2934,7 +3183,7 @@
         <v>345</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>345</v>
+        <v>293</v>
       </c>
       <c r="H34" s="5" t="n">
         <v>350</v>
@@ -2952,12 +3201,27 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>院线</t>
+          <t>校级专业线</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>2024年录取9人最低349最高420均分373；2025年录取47人均分351</t>
+          <t>105118复试线：2024年345、2025年执行A区线293、2026年350；2025年全校各培养单位合计录取49人</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>https://yjsy.wmu.edu.cn/info/1011/78011.htm</t>
+        </is>
+      </c>
+      <c r="O34" s="10" t="inlineStr">
+        <is>
+          <t>https://yjsy.wmu.edu.cn/info/3541/150531.htm</t>
+        </is>
+      </c>
+      <c r="P34" s="10" t="inlineStr">
+        <is>
+          <t>https://yjsy.wmu.edu.cn/</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3265,27 @@
       <c r="K35" s="5" t="n"/>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
           <t>2025年录取13人均分352</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O35" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P35" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -3056,12 +3335,27 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
           <t>2025年录取5人均分356</t>
+        </is>
+      </c>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O36" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P36" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -3113,6 +3407,9 @@
           <t>2024年录取6人均分334.8；2026年录取5人均分335.6</t>
         </is>
       </c>
+      <c r="N37" s="6" t="n"/>
+      <c r="O37" s="6" t="n"/>
+      <c r="P37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -3154,12 +3451,27 @@
       <c r="K38" s="5" t="n"/>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
           <t>2026年录取2人最低359；2025年录取3人均分344</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O38" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P38" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3515,27 @@
       <c r="K39" s="5" t="n"/>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
           <t>2025年录取47人均分360</t>
+        </is>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O39" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P39" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -3252,12 +3579,27 @@
       <c r="K40" s="5" t="n"/>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
           <t>2025年录取42人均分335</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O40" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P40" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -3301,12 +3643,27 @@
       <c r="K41" s="5" t="n"/>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
           <t>2025年录取29人均分349；2026年录取14人均分330</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O41" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P41" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -3350,12 +3707,27 @@
       <c r="K42" s="5" t="n"/>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
           <t>2025年录取61人均分359；2026年录取27人均分340</t>
+        </is>
+      </c>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O42" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P42" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -3399,12 +3771,27 @@
       <c r="K43" s="5" t="n"/>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
           <t>2025年录取14人均分342</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O43" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P43" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -3462,6 +3849,9 @@
           <t>2025年录取34人均分369；2026年麻醉学院线350</t>
         </is>
       </c>
+      <c r="N44" s="6" t="n"/>
+      <c r="O44" s="6" t="n"/>
+      <c r="P44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -3507,6 +3897,9 @@
           <t>2025年录取3人均分336</t>
         </is>
       </c>
+      <c r="N45" s="6" t="n"/>
+      <c r="O45" s="6" t="n"/>
+      <c r="P45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
@@ -3558,6 +3951,9 @@
           <t>1051专硕校线；2026年齐鲁医院麻醉专硕均分392</t>
         </is>
       </c>
+      <c r="N46" s="6" t="n"/>
+      <c r="O46" s="6" t="n"/>
+      <c r="P46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -3599,12 +3995,27 @@
       <c r="K47" s="5" t="n"/>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
           <t>2025年录取28人均分344</t>
+        </is>
+      </c>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O47" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P47" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -3648,12 +4059,27 @@
       <c r="K48" s="5" t="n"/>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
           <t>2025年录取30人均分342</t>
+        </is>
+      </c>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O48" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P48" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -3697,12 +4123,27 @@
       <c r="K49" s="5" t="n"/>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
           <t>2025年录取18人均分318，全国最低梯队</t>
+        </is>
+      </c>
+      <c r="N49" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O49" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P49" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -3746,12 +4187,27 @@
       <c r="K50" s="5" t="n"/>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
           <t>2025年录取22人均分352</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O50" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P50" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -3795,12 +4251,27 @@
       <c r="K51" s="5" t="n"/>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
           <t>2025年录取4人均分360</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O51" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P51" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -3856,6 +4327,9 @@
           <t>2026年第一临床370、第二临床340、第三临床312</t>
         </is>
       </c>
+      <c r="N52" s="6" t="n"/>
+      <c r="O52" s="6" t="n"/>
+      <c r="P52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -3884,7 +4358,9 @@
       <c r="F53" s="5" t="n">
         <v>343</v>
       </c>
-      <c r="G53" s="5" t="n"/>
+      <c r="G53" s="5" t="n">
+        <v>323</v>
+      </c>
       <c r="H53" s="5" t="n"/>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -3900,9 +4376,16 @@
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>2025年录取18人均分353</t>
-        </is>
-      </c>
+          <t>2025年105118复试线323；录取18人均分353</t>
+        </is>
+      </c>
+      <c r="N53" s="6" t="n"/>
+      <c r="O53" s="10" t="inlineStr">
+        <is>
+          <t>https://med.henu.edu.cn/__local/5/6E/5F/73D3DE978BAC281509E81880472_9AFEDED6_31B9B.pdf</t>
+        </is>
+      </c>
+      <c r="P53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
@@ -3948,6 +4431,9 @@
           <t>麻醉学专业排名全国第33位</t>
         </is>
       </c>
+      <c r="N54" s="6" t="n"/>
+      <c r="O54" s="6" t="n"/>
+      <c r="P54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -3993,6 +4479,9 @@
           <t>2025年录取19人均分352</t>
         </is>
       </c>
+      <c r="N55" s="6" t="n"/>
+      <c r="O55" s="6" t="n"/>
+      <c r="P55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
@@ -4038,6 +4527,9 @@
           <t>2025年录取8人均分362</t>
         </is>
       </c>
+      <c r="N56" s="6" t="n"/>
+      <c r="O56" s="6" t="n"/>
+      <c r="P56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
@@ -4079,12 +4571,27 @@
       <c r="K57" s="5" t="n"/>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
           <t>2025年录取19人均分324</t>
+        </is>
+      </c>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O57" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P57" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -4136,6 +4643,9 @@
           <t>2025年录取24人均分374；2026年湘雅医院一志愿录取最低约386</t>
         </is>
       </c>
+      <c r="N58" s="6" t="n"/>
+      <c r="O58" s="6" t="n"/>
+      <c r="P58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
@@ -4175,12 +4685,27 @@
       <c r="K59" s="5" t="n"/>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
           <t>2025年录取7人均分336</t>
+        </is>
+      </c>
+      <c r="N59" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O59" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P59" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -4228,6 +4753,9 @@
           <t>麻醉学专业排名全国第27位</t>
         </is>
       </c>
+      <c r="N60" s="6" t="n"/>
+      <c r="O60" s="6" t="n"/>
+      <c r="P60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
@@ -4273,6 +4801,9 @@
           <t>2025年录取25人均分378，含省医临床学院均分402</t>
         </is>
       </c>
+      <c r="N61" s="6" t="n"/>
+      <c r="O61" s="6" t="n"/>
+      <c r="P61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
@@ -4328,6 +4859,9 @@
           <t>2025年录取29人均分364；2026年各附属医院统一按310执行</t>
         </is>
       </c>
+      <c r="N62" s="6" t="n"/>
+      <c r="O62" s="6" t="n"/>
+      <c r="P62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -4383,6 +4917,9 @@
           <t>2026年第三临床医学院294（复试比1:2）；2025年录取14人均分354</t>
         </is>
       </c>
+      <c r="N63" s="6" t="n"/>
+      <c r="O63" s="6" t="n"/>
+      <c r="P63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
@@ -4428,6 +4965,9 @@
           <t>2025年录取27人均分354</t>
         </is>
       </c>
+      <c r="N64" s="6" t="n"/>
+      <c r="O64" s="6" t="n"/>
+      <c r="P64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
@@ -4477,6 +5017,9 @@
           <t>2025年录取31人均分354</t>
         </is>
       </c>
+      <c r="N65" s="6" t="n"/>
+      <c r="O65" s="6" t="n"/>
+      <c r="P65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
@@ -4524,6 +5067,9 @@
           <t>—</t>
         </is>
       </c>
+      <c r="N66" s="6" t="n"/>
+      <c r="O66" s="6" t="n"/>
+      <c r="P66" s="6" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
@@ -4569,6 +5115,9 @@
           <t>2025年录取9人均分353</t>
         </is>
       </c>
+      <c r="N67" s="6" t="n"/>
+      <c r="O67" s="6" t="n"/>
+      <c r="P67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
@@ -4624,6 +5173,9 @@
           <t>2026年麻醉学拟录取最低371、最高438、录取8人；2025年录取7人均分372</t>
         </is>
       </c>
+      <c r="N68" s="6" t="n"/>
+      <c r="O68" s="6" t="n"/>
+      <c r="P68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
@@ -4649,24 +5201,49 @@
           <t>985</t>
         </is>
       </c>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
+      <c r="F69" s="5" t="n">
+        <v>365</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>305</v>
+      </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="n"/>
+      <c r="J69" s="5" t="n">
+        <v>-60</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>院线</t>
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
-          <t>2025年录取10人均分372</t>
+          <t>105118复试线：2024年365、2025年360、2026年305；2025年录取10人均分372</t>
+        </is>
+      </c>
+      <c r="N69" s="10" t="inlineStr">
+        <is>
+          <t>https://yz.uestc.edu.cn/info/1082/5174.htm</t>
+        </is>
+      </c>
+      <c r="O69" s="10" t="inlineStr">
+        <is>
+          <t>https://yz.uestc.edu.cn/info/1082/5536.htm</t>
+        </is>
+      </c>
+      <c r="P69" s="10" t="inlineStr">
+        <is>
+          <t>https://yz.uestc.edu.cn/info/1082/5854.htm</t>
         </is>
       </c>
     </row>
@@ -4698,24 +5275,45 @@
         <v>306</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>293</v>
-      </c>
-      <c r="H70" s="5" t="n"/>
+        <v>351</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>325</v>
+      </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="n"/>
+      <c r="J70" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>31</v>
+      </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>院线</t>
         </is>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
-          <t>2025年录取26人均分371</t>
+          <t>105118复试线：2024年306、2025年351、2026年325；2025年录取26人均分371</t>
+        </is>
+      </c>
+      <c r="N70" s="10" t="inlineStr">
+        <is>
+          <t>https://yjs.swmu.edu.cn/info/1036/6819.htm</t>
+        </is>
+      </c>
+      <c r="O70" s="10" t="inlineStr">
+        <is>
+          <t>https://yjs.swmu.edu.cn/info/1014/8689.htm</t>
+        </is>
+      </c>
+      <c r="P70" s="10" t="inlineStr">
+        <is>
+          <t>https://yjs.swmu.edu.cn/info/1014/10689.htm</t>
         </is>
       </c>
     </row>
@@ -4767,6 +5365,9 @@
           <t>2026年录取30人均分358（区间295-399）</t>
         </is>
       </c>
+      <c r="N71" s="6" t="n"/>
+      <c r="O71" s="6" t="n"/>
+      <c r="P71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
@@ -4795,7 +5396,9 @@
       <c r="F72" s="5" t="n">
         <v>332</v>
       </c>
-      <c r="G72" s="5" t="n"/>
+      <c r="G72" s="5" t="n">
+        <v>320</v>
+      </c>
       <c r="H72" s="5" t="n"/>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -4811,9 +5414,20 @@
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
-          <t>2024年拟录取14人最低332</t>
-        </is>
-      </c>
+          <t>105118复试线：2024年332、2025年320</t>
+        </is>
+      </c>
+      <c r="N72" s="10" t="inlineStr">
+        <is>
+          <t>https://yjsy.cmc.edu.cn/info/1016/2102.htm</t>
+        </is>
+      </c>
+      <c r="O72" s="10" t="inlineStr">
+        <is>
+          <t>https://yjsy.cmc.edu.cn/info/1016/2287.htm</t>
+        </is>
+      </c>
+      <c r="P72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
@@ -4869,6 +5483,9 @@
           <t>2025年录取26人均分380，为西南最高；2026年降至335</t>
         </is>
       </c>
+      <c r="N73" s="6" t="n"/>
+      <c r="O73" s="6" t="n"/>
+      <c r="P73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
@@ -4914,6 +5531,9 @@
           <t>2025年录取3人均分372</t>
         </is>
       </c>
+      <c r="N74" s="6" t="n"/>
+      <c r="O74" s="6" t="n"/>
+      <c r="P74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
@@ -4969,6 +5589,9 @@
           <t>2025年录取21人均分349；2026年疼痛方向录取6人均分338</t>
         </is>
       </c>
+      <c r="N75" s="6" t="n"/>
+      <c r="O75" s="6" t="n"/>
+      <c r="P75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
@@ -5014,6 +5637,9 @@
           <t>2025年录取24人均分343</t>
         </is>
       </c>
+      <c r="N76" s="6" t="n"/>
+      <c r="O76" s="6" t="n"/>
+      <c r="P76" s="6" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
@@ -5069,6 +5695,9 @@
           <t>2025年录取42人均分349</t>
         </is>
       </c>
+      <c r="N77" s="6" t="n"/>
+      <c r="O77" s="6" t="n"/>
+      <c r="P77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
@@ -5118,6 +5747,9 @@
           <t>2025年录取4人均分325</t>
         </is>
       </c>
+      <c r="N78" s="6" t="n"/>
+      <c r="O78" s="6" t="n"/>
+      <c r="P78" s="6" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
@@ -5167,6 +5799,9 @@
           <t>2025年录取15人均分339</t>
         </is>
       </c>
+      <c r="N79" s="6" t="n"/>
+      <c r="O79" s="6" t="n"/>
+      <c r="P79" s="6" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
@@ -5216,6 +5851,9 @@
           <t>2026年校线330、麻醉学370，招生缩至6人；2025年录取10人均分374</t>
         </is>
       </c>
+      <c r="N80" s="6" t="n"/>
+      <c r="O80" s="6" t="n"/>
+      <c r="P80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
@@ -5257,12 +5895,27 @@
       <c r="K81" s="5" t="n"/>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
           <t>2025年录取18人均分341</t>
+        </is>
+      </c>
+      <c r="N81" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O81" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P81" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5947,7 @@
         <v>304</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="H82" s="5" t="n">
         <v>307</v>
@@ -5312,12 +5965,23 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>院自划线</t>
+          <t>院线</t>
         </is>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
-          <t>2026年延安医学院麻醉学307分</t>
+          <t>105118复试线：2024年304、2025年325、2026年307</t>
+        </is>
+      </c>
+      <c r="N82" s="6" t="n"/>
+      <c r="O82" s="10" t="inlineStr">
+        <is>
+          <t>https://yjsy.yau.edu.cn/info/1025/21240.htm</t>
+        </is>
+      </c>
+      <c r="P82" s="10" t="inlineStr">
+        <is>
+          <t>https://yjsy.yau.edu.cn/info/1025/40282.htm</t>
         </is>
       </c>
     </row>
@@ -5369,6 +6033,9 @@
           <t>2025年麻醉学专硕297分</t>
         </is>
       </c>
+      <c r="N83" s="6" t="n"/>
+      <c r="O83" s="6" t="n"/>
+      <c r="P83" s="6" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
@@ -5414,6 +6081,9 @@
           <t>2025年录取16人均分354；2026年一临录取16人最低328</t>
         </is>
       </c>
+      <c r="N84" s="6" t="n"/>
+      <c r="O84" s="6" t="n"/>
+      <c r="P84" s="6" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
@@ -5455,12 +6125,27 @@
       <c r="K85" s="5" t="n"/>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="N85" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O85" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P85" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -5502,12 +6187,27 @@
       <c r="K86" s="5" t="n"/>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="N86" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O86" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P86" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -5551,12 +6251,27 @@
       <c r="K87" s="5" t="n"/>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
           <t>2025年录取20人均分342；2026年第三临床15人均分342</t>
+        </is>
+      </c>
+      <c r="N87" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O87" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P87" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -5604,6 +6319,9 @@
           <t>2025年录取17人均分333</t>
         </is>
       </c>
+      <c r="N88" s="6" t="n"/>
+      <c r="O88" s="6" t="n"/>
+      <c r="P88" s="6" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
@@ -5645,12 +6363,27 @@
       <c r="K89" s="5" t="n"/>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
           <t>2025年录取62人均分324；2026年一临31人均分325</t>
+        </is>
+      </c>
+      <c r="N89" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O89" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P89" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -5698,6 +6431,9 @@
           <t>2025年录取3人均分320</t>
         </is>
       </c>
+      <c r="N90" s="6" t="n"/>
+      <c r="O90" s="6" t="n"/>
+      <c r="P90" s="6" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
@@ -5739,12 +6475,27 @@
       <c r="K91" s="5" t="n"/>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="N91" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O91" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P91" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -5786,12 +6537,27 @@
       <c r="K92" s="5" t="n"/>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（非院线）</t>
         </is>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="N92" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202403/W020240312598657688341.pdf</t>
+        </is>
+      </c>
+      <c r="O92" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202502/W020250224570852404019.pdf</t>
+        </is>
+      </c>
+      <c r="P92" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moe.gov.cn/jyb_xwfb/gzdt_gzdt/s5987/202602/W020260228373276320816.pdf</t>
         </is>
       </c>
     </row>
@@ -5839,13 +6605,182 @@
           <t>麻醉学专业排名全国第16位</t>
         </is>
       </c>
+      <c r="N93" s="6" t="n"/>
+      <c r="O93" s="6" t="n"/>
+      <c r="P93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="5" t="n"/>
+      <c r="H94" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>50/50/180</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="n"/>
+      <c r="K94" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>1051校基本线</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>300为临床医学专业学位校级基本线，不等同于105118院线；报考前须再核对医学院细则</t>
+        </is>
+      </c>
+      <c r="N94" s="6" t="n"/>
+      <c r="O94" s="6" t="n"/>
+      <c r="P94" s="10" t="inlineStr">
+        <is>
+          <t>https://yzb.nju.edu.cn/9c/f9/c47863a826617/page.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>大连理工大学</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>大连</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="n"/>
+      <c r="K95" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>院线</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>2026年105118复试线300，统考招生1人</t>
+        </is>
+      </c>
+      <c r="N95" s="6" t="n"/>
+      <c r="O95" s="6" t="n"/>
+      <c r="P95" s="10" t="inlineStr">
+        <is>
+          <t>https://med.dlut.edu.cn/info/1003/10789.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>吉首大学</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>吉首</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>省属</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>323</v>
+      </c>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="5" t="n"/>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="n"/>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>院线</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>2024年105118复试线323</t>
+        </is>
+      </c>
+      <c r="N96" s="10" t="inlineStr">
+        <is>
+          <t>https://yjsc.jsu.edu.cn/sylm/tzgg/cf5d235ba8634a249e7ca7e42cc19789.htm</t>
+        </is>
+      </c>
+      <c r="O96" s="6" t="n"/>
+      <c r="P96" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M93"/>
+  <autoFilter ref="A2:P96"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
-  <conditionalFormatting sqref="K3:K93">
+  <conditionalFormatting sqref="K3:K96">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>60</formula>
     </cfRule>
@@ -5857,7 +6792,7 @@
       <formula>30</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3:J93">
+  <conditionalFormatting sqref="J3:J96">
     <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -5865,6 +6800,123 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P57" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P69" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P70" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P81" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P82" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N85" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P85" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P86" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N87" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P87" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N89" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P89" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N91" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P91" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N92" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P92" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P94" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P95" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N96" r:id="rId115"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5876,7 +6928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5885,6 +6937,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -5925,6 +6978,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>官方来源</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -5953,6 +7011,7 @@
           <t>2026年拟录取最低371、最高438、录取8人</t>
         </is>
       </c>
+      <c r="G3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -5981,6 +7040,7 @@
           <t>2026年麻醉学专硕院线</t>
         </is>
       </c>
+      <c r="G4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -6009,6 +7069,7 @@
           <t>校级1051线330，麻醉学院线370；招生6人</t>
         </is>
       </c>
+      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -6037,6 +7098,7 @@
           <t>2025年该院录取13人均分381</t>
         </is>
       </c>
+      <c r="G6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -6065,6 +7127,7 @@
           <t>2026年专硕计划13人</t>
         </is>
       </c>
+      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -6093,6 +7156,7 @@
           <t>徐医麻醉学为全国第一（校友会A++）</t>
         </is>
       </c>
+      <c r="G8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -6121,6 +7185,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -6149,6 +7214,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -6177,6 +7243,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -6202,7 +7269,12 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>2024年345、2025年345，三年稳步上行</t>
+          <t>2024年345、2025年293、2026年350；年度已重新核对</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>https://yjsy.wmu.edu.cn/</t>
         </is>
       </c>
     </row>
@@ -6233,6 +7305,7 @@
           <t>2024年315，2026年大幅提至350</t>
         </is>
       </c>
+      <c r="G13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -6261,6 +7334,7 @@
           <t>校级1051线；齐鲁医院麻醉专硕均分392</t>
         </is>
       </c>
+      <c r="G14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -6289,6 +7363,7 @@
           <t>2026年录取3人，最低340</t>
         </is>
       </c>
+      <c r="G15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -6317,6 +7392,11 @@
           <t>2025年录取9人均分337</t>
         </is>
       </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>https://yz.jiangnan.edu.cn/info/1029/3750.htm</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -6345,6 +7425,7 @@
           <t>2024年365、2025年360，2026年回调至335</t>
         </is>
       </c>
+      <c r="G17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -6373,6 +7454,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -6401,6 +7483,7 @@
           <t>2024年321→2025年342→2026年332，高位盘整</t>
         </is>
       </c>
+      <c r="G19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -6429,6 +7512,7 @@
           <t>校级1051线；2025年录取12人均分358</t>
         </is>
       </c>
+      <c r="G20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -6457,6 +7541,7 @@
           <t>校级1051线</t>
         </is>
       </c>
+      <c r="G21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -6485,6 +7570,7 @@
           <t>2026年统考计划7人</t>
         </is>
       </c>
+      <c r="G22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -6492,16 +7578,16 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>牡丹江医科大学</t>
+          <t>西南医科大学</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>附属红旗医院规培基地</t>
+          <t>临床医学院</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -6510,7 +7596,12 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>复试比不低于1:1.2</t>
+          <t>2024年306、2025年351、2026年325</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>https://yjs.swmu.edu.cn/info/1014/10689.htm</t>
         </is>
       </c>
     </row>
@@ -6520,27 +7611,28 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>牡丹江医科大学</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>临床医学（1051）</t>
+          <t>附属红旗医院规培基地</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>50/50/180</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>校级1051线；麻醉统招约8人</t>
-        </is>
-      </c>
+          <t>复试比不低于1:1.2</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -6548,12 +7640,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>吉林大学</t>
+          <t>复旦大学</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>白求恩医学部（1051）</t>
+          <t>临床医学（1051）</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -6561,14 +7653,15 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50/50/180</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>2025年录取28人均分375</t>
-        </is>
-      </c>
+          <t>校级1051线；麻醉统招约8人</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -6576,27 +7669,28 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>贵州医科大学</t>
+          <t>吉林大学</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>麻醉学院</t>
+          <t>白求恩医学部（1051）</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>48/48/—</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>2026年疼痛方向录取6人均分338</t>
-        </is>
-      </c>
+          <t>2025年录取28人均分375</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -6604,27 +7698,28 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>昆明医科大学</t>
+          <t>贵州医科大学</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>不区分院系</t>
+          <t>麻醉学院</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>45/45/99</t>
+          <t>48/48/—</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>2024年325→2026年315</t>
-        </is>
-      </c>
+          <t>2026年疼痛方向录取6人均分338</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -6632,27 +7727,28 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>郑州大学</t>
+          <t>昆明医科大学</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第三临床医学院</t>
+          <t>不区分院系</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45/45/99</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>2026年录取4人，最低312</t>
-        </is>
-      </c>
+          <t>2024年325→2026年315</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -6660,27 +7756,28 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>中山大学</t>
+          <t>郑州大学</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>各附属医院统一执行</t>
+          <t>第三临床医学院</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>45/45/170</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>2026年专硕计划29人（不含推免）</t>
-        </is>
-      </c>
+          <t>2026年录取4人，最低312</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -6688,12 +7785,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>北京大学医学部</t>
+          <t>中山大学</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>医学门类专硕（1051）</t>
+          <t>各附属医院统一执行</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
@@ -6701,14 +7798,15 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>55/55/180</t>
+          <t>45/45/170</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>校级线；实际录取远高于此</t>
-        </is>
-      </c>
+          <t>2026年专硕计划29人（不含推免）</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -6716,12 +7814,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>中南大学</t>
+          <t>北京大学医学部</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>临床医学（1051）</t>
+          <t>医学门类专硕（1051）</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
@@ -6729,14 +7827,15 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55/55/180</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>2026年湘雅医院一志愿录取最低约386</t>
-        </is>
-      </c>
+          <t>校级线；实际录取远高于此</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -6744,16 +7843,16 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>延安大学</t>
+          <t>中南大学</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>延安医学院</t>
+          <t>临床医学（1051）</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -6762,9 +7861,10 @@
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>2026年麻醉学自划线307</t>
-        </is>
-      </c>
+          <t>2026年湘雅医院一志愿录取最低约386</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -6772,16 +7872,16 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>大连理工大学</t>
+          <t>延安大学</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>医学部</t>
+          <t>延安医学院</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -6790,7 +7890,12 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>2026年招生1人</t>
+          <t>2026年麻醉学自划线307</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>https://yjsy.yau.edu.cn/info/1025/40282.htm</t>
         </is>
       </c>
     </row>
@@ -6800,25 +7905,30 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>暨南大学</t>
+          <t>电子科技大学</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第三临床医学院</t>
+          <t>医学院</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>36/36/108</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>2026年复试比1:2，统招计划1人</t>
+          <t>2024年365、2025年360、2026年305</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>https://yz.uestc.edu.cn/info/1082/5854.htm</t>
         </is>
       </c>
     </row>
@@ -6828,16 +7938,16 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>中国医科大学</t>
+          <t>大连理工大学</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>临床医学（1051）</t>
+          <t>医学部</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -6846,7 +7956,12 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>校级线；306单科要求170分</t>
+          <t>2026年招生1人</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>https://med.dlut.edu.cn/info/1003/10789.htm</t>
         </is>
       </c>
     </row>
@@ -6856,12 +7971,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>江苏大学</t>
+          <t>暨南大学</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>医学院</t>
+          <t>第三临床医学院</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
@@ -6874,9 +7989,10 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>执行国家A线；2026年招生7人</t>
-        </is>
-      </c>
+          <t>2026年复试比1:2，统招计划1人</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -6884,12 +8000,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>扬州大学</t>
+          <t>中国医科大学</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>医学院</t>
+          <t>临床医学（1051）</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
@@ -6897,14 +8013,15 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>36/36/108</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>执行国家A线</t>
-        </is>
-      </c>
+          <t>校级线；306单科要求170分</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -6912,12 +8029,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>湖州师范学院</t>
+          <t>江苏大学</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>医学院、护理学院</t>
+          <t>医学院</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
@@ -6930,7 +8047,12 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>执行国家A线；招生3人</t>
+          <t>执行国家A线；2026年招生7人</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>https://yz.ujs.edu.cn/info/1014/8467.htm</t>
         </is>
       </c>
     </row>
@@ -6940,32 +8062,91 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
+          <t>扬州大学</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>医学院</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>294</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>36/36/108</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>执行国家A线</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>湖州师范学院</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>医学院、护理学院</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>294</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>36/36/108</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>执行国家A线；招生3人</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
           <t>天津医科大学</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>临床医学部</t>
         </is>
       </c>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>50/50/170</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>2026年分数线未公布；计划招生17人（较2025年10人扩招70%）</t>
         </is>
       </c>
+      <c r="G41" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F39"/>
+  <autoFilter ref="A2:G41"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D3:D39">
+  <conditionalFormatting sqref="D3:D41">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6977,6 +8158,15 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6988,7 +8178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I153"/>
+  <dimension ref="A1:I154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9719,7 +10909,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F82" s="5" t="n">
         <v>397</v>
@@ -9730,7 +10920,11 @@
       <c r="H82" s="5" t="n">
         <v>342</v>
       </c>
-      <c r="I82" s="6" t="inlineStr"/>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>官方2025录取统计表</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
@@ -9776,27 +10970,31 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>宁波大学</t>
+          <t>温州医科大学</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>不区分院系所</t>
+          <t>台州医院</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>389</v>
+        <v>328</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>352</v>
-      </c>
-      <c r="I84" s="6" t="inlineStr"/>
+        <v>328</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>官方2025录取统计表</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
@@ -9809,7 +11007,7 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>湖州师范学院</t>
+          <t>宁波大学</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -9818,16 +11016,16 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>347</v>
+        <v>307</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I85" s="6" t="inlineStr"/>
     </row>
@@ -9842,7 +11040,7 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>绍兴文理学院</t>
+          <t>湖州师范学院</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -9854,19 +11052,15 @@
         <v>5</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>346</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>2024年录取6人均分334.8</t>
-        </is>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
@@ -9879,29 +11073,29 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>福建医科大学</t>
+          <t>绍兴文理学院</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>临床医学部</t>
+          <t>不区分院系所</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>398</v>
+        <v>357</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>2026年院线提至350</t>
+          <t>2024年录取6人均分334.8</t>
         </is>
       </c>
     </row>
@@ -9921,22 +11115,26 @@
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>福总临床医学院</t>
+          <t>临床医学部</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="G88" s="5" t="n">
         <v>345</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>372</v>
-      </c>
-      <c r="I88" s="6" t="inlineStr"/>
+        <v>366</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>2026年院线提至350</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
@@ -9954,17 +11152,17 @@
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>第一临床医学院</t>
+          <t>福总临床医学院</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="H89" s="5" t="n">
         <v>372</v>
@@ -9987,20 +11185,20 @@
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>协和临床医学院</t>
+          <t>第一临床医学院</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I90" s="6" t="inlineStr"/>
     </row>
@@ -10020,24 +11218,22 @@
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>省立临床医学院</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="n"/>
+          <t>协和临床医学院</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="F91" s="5" t="n">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>370</v>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>原表未列录取人数</t>
-        </is>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
@@ -10050,27 +11246,29 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>厦门大学</t>
+          <t>福建医科大学</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>不区分院系所</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="n">
-        <v>3</v>
-      </c>
+          <t>省立临床医学院</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n"/>
       <c r="F92" s="5" t="n">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>336</v>
-      </c>
-      <c r="I92" s="6" t="inlineStr"/>
+        <v>370</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>原表未列录取人数</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
@@ -10078,36 +11276,32 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>中南大学</t>
+          <t>厦门大学</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>湘雅医院</t>
+          <t>不区分院系所</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>399</v>
+        <v>357</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>351</v>
+        <v>304</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>378</v>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>2026年一志愿录取最低约386</t>
-        </is>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
@@ -10125,22 +11319,26 @@
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>湘雅三医院</t>
+          <t>湘雅医院</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>367</v>
-      </c>
-      <c r="I94" s="6" t="inlineStr"/>
+        <v>378</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>2026年一志愿录取最低约386</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
@@ -10158,20 +11356,20 @@
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>湘雅二医院</t>
+          <t>湘雅三医院</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F95" s="5" t="n">
+        <v>382</v>
+      </c>
+      <c r="G95" s="5" t="n">
         <v>358</v>
       </c>
-      <c r="G95" s="5" t="n">
-        <v>354</v>
-      </c>
       <c r="H95" s="5" t="n">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="I95" s="6" t="inlineStr"/>
     </row>
@@ -10186,25 +11384,25 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>武汉大学</t>
+          <t>中南大学</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>第一临床学院</t>
+          <t>湘雅二医院</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="I96" s="6" t="inlineStr"/>
     </row>
@@ -10224,20 +11422,20 @@
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>第二临床学院</t>
+          <t>第一临床学院</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="I97" s="6" t="inlineStr"/>
     </row>
@@ -10252,22 +11450,22 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>华中科技大学</t>
+          <t>武汉大学</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>第二临床学院（附属同济医院）</t>
+          <t>第二临床学院</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="H98" s="5" t="n">
         <v>356</v>
@@ -10290,20 +11488,20 @@
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>第一临床学院（附属协和医院）</t>
+          <t>第二临床学院（附属同济医院）</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="I99" s="6" t="inlineStr"/>
     </row>
@@ -10323,20 +11521,20 @@
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>附属武汉中心医院</t>
+          <t>第一临床学院（附属协和医院）</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I100" s="6" t="inlineStr"/>
     </row>
@@ -10356,20 +11554,20 @@
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>中部战区总医院</t>
+          <t>附属武汉中心医院</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="I101" s="6" t="inlineStr"/>
     </row>
@@ -10384,25 +11582,25 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>湖北医药学院</t>
+          <t>华中科技大学</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>第一临床学院</t>
+          <t>中部战区总医院</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>309</v>
+        <v>348</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="I102" s="6" t="inlineStr"/>
     </row>
@@ -10422,20 +11620,20 @@
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>第三临床学院</t>
+          <t>第一临床学院</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="I103" s="6" t="inlineStr"/>
     </row>
@@ -10455,24 +11653,22 @@
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>第四临床学院（湖北襄阳）</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="n"/>
+          <t>第三临床学院</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="F104" s="5" t="n">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>318</v>
-      </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>原表未列录取人数</t>
-        </is>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
@@ -10490,22 +11686,24 @@
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>荆门市中心医院</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>第四临床学院（湖北襄阳）</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n"/>
       <c r="F105" s="5" t="n">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>295</v>
-      </c>
-      <c r="I105" s="6" t="inlineStr"/>
+        <v>318</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>原表未列录取人数</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
@@ -10513,30 +11711,30 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>东北</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>中国医科大学</t>
+          <t>湖北医药学院</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>第一临床学院</t>
+          <t>荆门市中心医院</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>417</v>
+        <v>295</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>340</v>
+        <v>295</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>370</v>
+        <v>295</v>
       </c>
       <c r="I106" s="6" t="inlineStr"/>
     </row>
@@ -10556,20 +11754,20 @@
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>第二临床学院</t>
+          <t>第一临床学院</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
         <v>17</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I107" s="6" t="inlineStr"/>
     </row>
@@ -10589,20 +11787,20 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>第四临床学院</t>
+          <t>第二临床学院</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>368</v>
+        <v>406</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="I108" s="6" t="inlineStr"/>
     </row>
@@ -10622,20 +11820,20 @@
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>北部战区总医院</t>
+          <t>第四临床学院</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="I109" s="6" t="inlineStr"/>
     </row>
@@ -10655,20 +11853,20 @@
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>不区分院系所</t>
+          <t>北部战区总医院</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="I110" s="6" t="inlineStr"/>
     </row>
@@ -10683,25 +11881,25 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>大连医科大学</t>
+          <t>中国医科大学</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>附属第一医院</t>
+          <t>不区分院系所</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>380</v>
+        <v>322</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="I111" s="6" t="inlineStr"/>
     </row>
@@ -10721,20 +11919,20 @@
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>附属第二医院</t>
+          <t>附属第一医院</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I112" s="6" t="inlineStr"/>
     </row>
@@ -10749,25 +11947,25 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>锦州医科大学</t>
+          <t>大连医科大学</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>不区分院系所</t>
+          <t>附属第二医院</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="I113" s="6" t="inlineStr"/>
     </row>
@@ -10782,25 +11980,25 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>吉林大学</t>
+          <t>锦州医科大学</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>第三临床医学院</t>
+          <t>不区分院系所</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>360</v>
+        <v>307</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>378</v>
+        <v>332</v>
       </c>
       <c r="I114" s="6" t="inlineStr"/>
     </row>
@@ -10820,20 +12018,20 @@
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>第一临床医学院</t>
+          <t>第三临床医学院</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="I115" s="6" t="inlineStr"/>
     </row>
@@ -10853,20 +12051,20 @@
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>第二临床医学院</t>
+          <t>第一临床医学院</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>326</v>
+        <v>395</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>326</v>
+        <v>375</v>
       </c>
       <c r="I116" s="6" t="inlineStr"/>
     </row>
@@ -10881,25 +12079,25 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>延边大学</t>
+          <t>吉林大学</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>不区分院系所</t>
+          <t>第二临床医学院</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>391</v>
+        <v>326</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="I117" s="6" t="inlineStr"/>
     </row>
@@ -10914,25 +12112,25 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>哈尔滨医科大学</t>
+          <t>延边大学</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>第三临床医学院</t>
+          <t>不区分院系所</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>342</v>
+        <v>309</v>
       </c>
       <c r="H118" s="5" t="n">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="I118" s="6" t="inlineStr"/>
     </row>
@@ -10952,20 +12150,20 @@
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>第二临床医学院</t>
+          <t>第三临床医学院</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="I119" s="6" t="inlineStr"/>
     </row>
@@ -10985,20 +12183,20 @@
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>第一临床医学院</t>
+          <t>第二临床医学院</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="I120" s="6" t="inlineStr"/>
     </row>
@@ -11018,24 +12216,22 @@
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>第四临床医学院</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="n"/>
+          <t>第一临床医学院</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="F121" s="5" t="n">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>381</v>
+        <v>341</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>381</v>
-      </c>
-      <c r="I121" s="6" t="inlineStr">
-        <is>
-          <t>原表未列录取人数</t>
-        </is>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
@@ -11048,27 +12244,27 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>佳木斯大学</t>
+          <t>哈尔滨医科大学</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>临床医学院</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F122" s="5" t="n"/>
+          <t>第四临床医学院</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n"/>
+      <c r="F122" s="5" t="n">
+        <v>381</v>
+      </c>
       <c r="G122" s="5" t="n">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>原表数据不完整，最低/平均分存疑</t>
+          <t>原表未列录取人数</t>
         </is>
       </c>
     </row>
@@ -11078,34 +12274,32 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>东北</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>南方医科大学</t>
+          <t>佳木斯大学</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>省医临床学院</t>
+          <t>临床医学院</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F123" s="5" t="n">
-        <v>414</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F123" s="5" t="n"/>
       <c r="G123" s="5" t="n">
-        <v>391</v>
+        <v>356</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>402</v>
+        <v>369</v>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>全校均分最高院区</t>
+          <t>原表数据不完整，最低/平均分存疑</t>
         </is>
       </c>
     </row>
@@ -11125,22 +12319,26 @@
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>第二临床学院</t>
+          <t>省医临床学院</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="H124" s="5" t="n">
-        <v>384</v>
-      </c>
-      <c r="I124" s="6" t="inlineStr"/>
+        <v>402</v>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>全校均分最高院区</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
@@ -11158,20 +12356,20 @@
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>第一临床学院</t>
+          <t>第二临床学院</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="H125" s="5" t="n">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="I125" s="6" t="inlineStr"/>
     </row>
@@ -11191,20 +12389,20 @@
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>第三临床学院</t>
+          <t>第一临床学院</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H126" s="5" t="n">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="I126" s="6" t="inlineStr"/>
     </row>
@@ -11219,25 +12417,25 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>广东医科大学</t>
+          <t>南方医科大学</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>不区分院系所</t>
+          <t>第三临床学院</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="I127" s="6" t="inlineStr"/>
     </row>
@@ -11252,7 +12450,7 @@
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>广州医科大学</t>
+          <t>广东医科大学</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
@@ -11261,13 +12459,13 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="H128" s="5" t="n">
         <v>354</v>
@@ -11285,25 +12483,25 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>暨南大学</t>
+          <t>广州医科大学</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>第一临床医学院</t>
+          <t>不区分院系所</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I129" s="6" t="inlineStr"/>
     </row>
@@ -11323,20 +12521,20 @@
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>第二临床医学院</t>
+          <t>第一临床医学院</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="H130" s="5" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I130" s="6" t="inlineStr"/>
     </row>
@@ -11356,20 +12554,20 @@
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>广州市红十字会医院</t>
+          <t>第二临床医学院</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>350</v>
+        <v>383</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="H131" s="5" t="n">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="I131" s="6" t="inlineStr"/>
     </row>
@@ -11384,25 +12582,25 @@
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>海南医科大学</t>
+          <t>暨南大学</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>不区分院系所</t>
+          <t>广州市红十字会医院</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="H132" s="5" t="n">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="I132" s="6" t="inlineStr"/>
     </row>
@@ -11412,36 +12610,32 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>四川大学</t>
+          <t>海南医科大学</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>临床医学院（华西）</t>
+          <t>不区分院系所</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="H133" s="5" t="n">
-        <v>372</v>
-      </c>
-      <c r="I133" s="6" t="inlineStr">
-        <is>
-          <t>2026年录取8人最低371最高438</t>
-        </is>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="I133" s="6" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
@@ -11454,27 +12648,31 @@
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>电子科技大学</t>
+          <t>四川大学</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>不区分院系所</t>
+          <t>临床医学院（华西）</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H134" s="5" t="n">
         <v>372</v>
       </c>
-      <c r="I134" s="6" t="inlineStr"/>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>2026年录取8人最低371最高438</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
@@ -11487,7 +12685,7 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>西南医科大学</t>
+          <t>电子科技大学</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -11496,16 +12694,16 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="H135" s="5" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I135" s="6" t="inlineStr"/>
     </row>
@@ -11520,7 +12718,7 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>川北医学院</t>
+          <t>西南医科大学</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -11529,22 +12727,18 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="H136" s="5" t="n">
-        <v>359</v>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
-        <is>
-          <t>2026年录取30人均分358</t>
-        </is>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="I136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
@@ -11557,7 +12751,7 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>重庆医科大学</t>
+          <t>川北医学院</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
@@ -11566,20 +12760,20 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="H137" s="5" t="n">
-        <v>380</v>
+        <v>359</v>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>西南地区录取均分最高</t>
+          <t>2026年录取30人均分358</t>
         </is>
       </c>
     </row>
@@ -11594,7 +12788,7 @@
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>陆军军医大学</t>
+          <t>重庆医科大学</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -11603,18 +12797,22 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>381</v>
+        <v>410</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H138" s="5" t="n">
-        <v>372</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr"/>
+        <v>380</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>西南地区录取均分最高</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
@@ -11627,7 +12825,7 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>贵州医科大学</t>
+          <t>陆军军医大学</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -11636,16 +12834,16 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>319</v>
+        <v>363</v>
       </c>
       <c r="H139" s="5" t="n">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="I139" s="6" t="inlineStr"/>
     </row>
@@ -11660,25 +12858,25 @@
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>遵义医科大学</t>
+          <t>贵州医科大学</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>第一临床学院</t>
+          <t>不区分院系所</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="H140" s="5" t="n">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="I140" s="6" t="inlineStr"/>
     </row>
@@ -11693,25 +12891,25 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>昆明医科大学</t>
+          <t>遵义医科大学</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>不区分院系所</t>
+          <t>第一临床学院</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="H141" s="5" t="n">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="I141" s="6" t="inlineStr"/>
     </row>
@@ -11726,7 +12924,7 @@
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>昆明理工大学</t>
+          <t>昆明医科大学</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
@@ -11735,16 +12933,16 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="H142" s="5" t="n">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="I142" s="6" t="inlineStr"/>
     </row>
@@ -11754,12 +12952,12 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>西北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>西安交通大学</t>
+          <t>昆明理工大学</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
@@ -11768,22 +12966,18 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>385</v>
+        <v>354</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>347</v>
+        <v>286</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>374</v>
-      </c>
-      <c r="I143" s="6" t="inlineStr">
-        <is>
-          <t>2026年招生缩至6人</t>
-        </is>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
@@ -11796,7 +12990,7 @@
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>西安医学院</t>
+          <t>西安交通大学</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
@@ -11805,18 +12999,22 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="H144" s="5" t="n">
-        <v>341</v>
-      </c>
-      <c r="I144" s="6" t="inlineStr"/>
+        <v>374</v>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>2026年招生缩至6人</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
@@ -11829,7 +13027,7 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>青海大学</t>
+          <t>西安医学院</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
@@ -11838,16 +13036,16 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F145" s="5" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="H145" s="5" t="n">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="I145" s="6" t="inlineStr"/>
     </row>
@@ -11862,25 +13060,25 @@
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>宁夏医科大学</t>
+          <t>青海大学</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>第一临床医学院</t>
+          <t>不区分院系所</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="H146" s="5" t="n">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="I146" s="6" t="inlineStr"/>
     </row>
@@ -11900,26 +13098,22 @@
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>第三临床医学院</t>
+          <t>第一临床医学院</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F147" s="5" t="n">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="H147" s="5" t="n">
-        <v>330</v>
-      </c>
-      <c r="I147" s="6" t="inlineStr">
-        <is>
-          <t>2026年录取15人均分342</t>
-        </is>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n">
@@ -11932,29 +13126,29 @@
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>兰州大学</t>
+          <t>宁夏医科大学</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>第一临床医学院</t>
+          <t>第三临床医学院</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>376</v>
+        <v>355</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>334</v>
+        <v>294</v>
       </c>
       <c r="H148" s="5" t="n">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
-          <t>2026年录取16人最低328</t>
+          <t>2026年录取15人均分342</t>
         </is>
       </c>
     </row>
@@ -11974,22 +13168,26 @@
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>第二临床医学院</t>
+          <t>第一临床医学院</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="H149" s="5" t="n">
-        <v>364</v>
-      </c>
-      <c r="I149" s="6" t="inlineStr"/>
+        <v>351</v>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>2026年录取16人最低328</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n">
@@ -12002,31 +13200,27 @@
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>新疆医科大学</t>
+          <t>兰州大学</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>第一临床医学院</t>
+          <t>第二临床医学院</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>285</v>
+        <v>359</v>
       </c>
       <c r="H150" s="5" t="n">
-        <v>319</v>
-      </c>
-      <c r="I150" s="6" t="inlineStr">
-        <is>
-          <t>2026年录取31人均分325</t>
-        </is>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
@@ -12044,22 +13238,26 @@
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>第三临床医学院</t>
+          <t>第一临床医学院</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>332</v>
-      </c>
-      <c r="I151" s="6" t="inlineStr"/>
+        <v>319</v>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>2026年录取31人均分325</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n">
@@ -12077,20 +13275,20 @@
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区人民医院</t>
+          <t>第三临床医学院</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="H152" s="5" t="n">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="I152" s="6" t="inlineStr"/>
     </row>
@@ -12110,29 +13308,62 @@
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
+          <t>新疆维吾尔自治区人民医院</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>354</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>283</v>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>323</v>
+      </c>
+      <c r="I153" s="6" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>西北</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>新疆医科大学</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
           <t>第二临床医学院</t>
         </is>
       </c>
-      <c r="E153" s="5" t="n">
+      <c r="E154" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F153" s="5" t="n">
+      <c r="F154" s="5" t="n">
         <v>339</v>
       </c>
-      <c r="G153" s="5" t="n">
+      <c r="G154" s="5" t="n">
         <v>310</v>
       </c>
-      <c r="H153" s="5" t="n">
+      <c r="H154" s="5" t="n">
         <v>325</v>
       </c>
-      <c r="I153" s="6" t="inlineStr"/>
+      <c r="I154" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I153"/>
+  <autoFilter ref="A2:I154"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H3:H153">
+  <conditionalFormatting sqref="H3:H154">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -12155,7 +13386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13425,7 +14656,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>42</v>
@@ -13438,7 +14669,7 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>院线（麻醉学院）</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
@@ -13480,7 +14711,7 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
@@ -13522,7 +14753,7 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
@@ -13564,7 +14795,7 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
@@ -13606,7 +14837,7 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
@@ -13648,7 +14879,7 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
@@ -13690,7 +14921,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
@@ -13732,7 +14963,7 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
@@ -13774,7 +15005,7 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
@@ -13816,7 +15047,7 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
@@ -13858,7 +15089,7 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
@@ -13900,7 +15131,7 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
@@ -13942,7 +15173,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
@@ -13984,7 +15215,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
@@ -14026,7 +15257,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
@@ -14068,7 +15299,7 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
@@ -14110,7 +15341,7 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
@@ -14152,7 +15383,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
@@ -14194,7 +15425,7 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
@@ -14236,7 +15467,7 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J50" s="6" t="inlineStr">
@@ -14278,7 +15509,7 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
@@ -14320,7 +15551,7 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J52" s="6" t="inlineStr">
@@ -14362,7 +15593,7 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
@@ -14404,7 +15635,7 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
@@ -14446,7 +15677,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
@@ -14488,7 +15719,7 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J56" s="6" t="inlineStr">
@@ -14530,7 +15761,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
@@ -14572,7 +15803,7 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>国家A线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
@@ -14614,7 +15845,7 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
@@ -14656,7 +15887,7 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
@@ -14671,17 +15902,17 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>延边大学</t>
+          <t>内蒙古医科大学</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>延吉</t>
+          <t>呼和浩特</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -14698,12 +15929,12 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B区</t>
         </is>
       </c>
     </row>
@@ -14713,7 +15944,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>内蒙古医科大学</t>
+          <t>内蒙古科技大学</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -14723,7 +15954,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>呼和浩特</t>
+          <t>包头</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
@@ -14740,7 +15971,7 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J62" s="6" t="inlineStr">
@@ -14755,7 +15986,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>内蒙古科技大学</t>
+          <t>内蒙古民族大学</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -14765,7 +15996,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>包头</t>
+          <t>通辽</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
@@ -14782,7 +16013,7 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
@@ -14797,17 +16028,17 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>内蒙古民族大学</t>
+          <t>甘肃中医药大学</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>通辽</t>
+          <t>兰州</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
@@ -14824,7 +16055,7 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J64" s="6" t="inlineStr">
@@ -14839,7 +16070,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>甘肃中医药大学</t>
+          <t>西北民族大学</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -14866,7 +16097,7 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
@@ -14881,17 +16112,17 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>西北民族大学</t>
+          <t>新疆医科大学</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>兰州</t>
+          <t>乌鲁木齐</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -14908,7 +16139,7 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J66" s="6" t="inlineStr">
@@ -14923,17 +16154,17 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>新疆医科大学</t>
+          <t>右江民族医学院</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐</t>
+          <t>百色</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
@@ -14950,7 +16181,7 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>国家B线</t>
+          <t>教育部参考线（未核院线）</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
@@ -14959,50 +16190,8 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>右江民族医学院</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>百色</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>294</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>国家B线</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>B区</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:J68"/>
+  <autoFilter ref="A2:J67"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -15489,7 +16678,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2025年录取47人均分351</t>
+          <t>2025年各培养单位合计录取49人，统考初试加权均分约351</t>
         </is>
       </c>
     </row>
@@ -16265,297 +17454,297 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>一、专业代码口径</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>105118</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>麻醉学（专业学位硕士），隶属临床医学专业学位类别（1051）。学术型硕士对应代码为 100217 麻醉学。本表数据默认指 105118 专业学位。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>考试科目</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>政治(101) + 英语一(201) + 306 临床医学综合能力（西医，满分300），初试总分 500 分。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>划线机制</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>临床医学类专业学位（1051、1052、1057）的复试线由各招生单位自主确定，教育部只公布参考性的国家线。因此同一专业不同院校、甚至同一院校不同附属医院之间分数差异极大。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>院校所在地</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>「地区」列为院校所属省级行政区，「城市」列为院校所在（主校区/研究生培养）地级市。直辖市地区与城市同名；中国香港/中国澳门/中国台湾未收录。个别院校多校区办学（如滨州医学院在烟台、滨州两地），城市列取考研院校代码库口径的主校区城市，实际培养校区请以当年招生简章为准。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr"/>
+      <c r="A8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>二、三年国家线（临床医学类专硕，与医学门类同线）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>2024 年</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>A 区 304 分（单科 42 / 126）；B 区 294 分（单科 39 / 117）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>2025 年</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>A 区 293 分（单科 36 / 108）；B 区 283 分（单科 33 / 99）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>2026 年</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>A 区 294 分（单科 36 / 108）；B 区 284 分（单科 33 / 99）</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr"/>
+      <c r="A13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>三、表内「复试线」与「录取分」的区别（关键）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>复试线</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>进入复试的最低初试总分门槛，由院校/学院自行划定，差额比例一般不低于 1:1.2，部分院校达 1:2。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>录取最低分 / 平均分</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>实际拟录取考生的初试分数，通常显著高于复试线（头部院校可高 30~60 分）。择校时应以录取分为主要参考。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>校线 vs 院线</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>「校线」为学校对 1051 一级学科的划线（如复旦 320、交大 330、首都医科 330）；「院线」为具体学院/基地按生源单独划的线（如郑州大学第一临床医学院 370）。表内已用「数据性质」列区分。</t>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>四类分数须分开</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>教育部参考线只用于说明A/B区最低基准，不自动等于院校105118复试线；校线是1051类别基本线；院线/专业线是具体学院或105118口径；录取最低分来自拟录取名单。四者不得混写。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr"/>
+      <c r="A18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>四、数据来源</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>官方来源</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>各院校研究生院/研究生招生网公布的复试分数线公告、拟录取名单、招生专业目录（如四川大学 yz.scu.edu.cn、上海交通大学 yzb.sjtu.edu.cn、福建医科大学 yjsy.fjmu.edu.cn、江苏大学 yz.ujs.edu.cn、中南大学湘雅医院、首都医科大学、徐州医科大学等）。</t>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>三年复试线表按院校+年度分别绑定来源链接；国家A/B区分数只引用教育部公告。找不到院校官方公告的国家线同分项标作“教育部参考线（非院线）”，不再冒充院校复试线。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>教育部/研招网</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>全国硕士研究生招生考试考生进入复试的初试成绩基本要求（2024/2025/2026 年，yz.chsi.com.cn）。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>第三方整理</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>启航考研、中公考研、新东方在线、路灯考研、掌上考研、宏医教育等平台按官网数据整理的院校分数线与报录比汇总表；2025 年录取明细（录取人数/最高/最低/平均分）来自医学考研类公众号对 90+ 培养单位拟录取名单的不完全统计。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>排名来源</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>软科 2025 中国大学专业排名（麻醉学，33 所上榜）、校友会 2025 中国大学一流专业排名（研究型）。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr"/>
+      <c r="A24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>五、使用须知与免责</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>数据时效</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>覆盖 2024、2025、2026 三个考研年度（分别对应 2023 年 12 月、2024 年 12 月、2025 年 12 月初试）。2026 年部分院校尚未公布复试线或拟录取数据，表中以空白表示。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>统计口径差异</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>部分院校按 1051 一级学科统一划线，未单列 105118，表内已标注「校线」；部分院校按附属医院/临床学院分别划线，已尽可能拆分到培养单位层级。</t>
         </is>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>可能存在误差</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>第三方整理数据存在少量错漏（如个别培养单位录取人数或最高分缺失、个别年份分数线口径不一致），报考前请务必以目标院校研究生院官网最新公告为唯一依据。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>建议用法</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>① 先用「三年复试线对比」筛选分数区间与目标层次；② 再用「2025录取明细」核对目标培养单位的实际录取分与招生规模；③ 结合「麻醉学专业排名」判断学科实力；④ 以「2026复试线明细」确认最新门槛。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr"/>
+      <c r="A30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>六、制表说明</t>
         </is>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>生成日期</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>总览看板 / 三年复试线对比 / 2026复试线明细 / 2025录取明细 / 2024复试线明细 / 麻醉学专业排名 / 数据来源与说明</t>
         </is>
